--- a/V9_W8_B32/data_instructions/VLIW_Excel/Unit6_to_12_ShuffleUnit.xlsx
+++ b/V9_W8_B32/data_instructions/VLIW_Excel/Unit6_to_12_ShuffleUnit.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\legoa\NCU\專題\專題內容\組譯器\WeightBiasRearranger\V7\data_instructions\VLIW_Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\legoa\NCU\專題\專題內容\組譯器\WeightBiasRearranger\V9_W8_B32\data_instructions\VLIW_Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D65F5FF-1B93-4C69-8F8B-4F1DD178841E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDC2603B-84A5-4A25-B984-07E4AF118742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{78D60548-BA91-4173-9352-325C39DD31E5}"/>
+    <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="12863" xr2:uid="{78D60548-BA91-4173-9352-325C39DD31E5}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -137,10 +137,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>記得存後半</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>記得放後半</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -394,6 +390,10 @@
   </si>
   <si>
     <t>8*(96/4)*7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Requant_Sel[3]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -645,16 +645,37 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -666,28 +687,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1075,7 +1075,7 @@
         <v>8</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>9</v>
@@ -1152,42 +1152,42 @@
         <v>23</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="N5" t="s">
+        <v>79</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="O5" t="s">
         <v>24</v>
       </c>
-      <c r="O5" t="s">
+      <c r="Q5" t="s">
         <v>25</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="7" spans="2:22">
       <c r="B7" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="31" t="s">
+      <c r="D7" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="19"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+      <c r="L7" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="M7" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="21"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="21"/>
-      <c r="I7" s="21"/>
-      <c r="J7" s="21"/>
-      <c r="L7" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="M7" s="9" t="s">
+      <c r="N7" s="9" t="s">
         <v>30</v>
-      </c>
-      <c r="N7" s="9" t="s">
-        <v>31</v>
       </c>
       <c r="O7" s="9">
         <v>0</v>
@@ -1205,62 +1205,62 @@
       <c r="B8">
         <v>0</v>
       </c>
-      <c r="C8" s="21"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="21"/>
-      <c r="H8" s="21"/>
-      <c r="I8" s="21"/>
-      <c r="J8" s="21"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="19"/>
       <c r="L8" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M8" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N8" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P8" s="17">
         <v>0</v>
       </c>
       <c r="Q8" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R8" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S8" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="T8" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="U8" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="V8" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="2:22">
-      <c r="C9" s="21"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="21"/>
-      <c r="J9" s="21"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
       <c r="L9" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M9" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N9" s="10"/>
       <c r="O9" s="10"/>
@@ -1272,23 +1272,23 @@
       <c r="U9" s="10"/>
     </row>
     <row r="10" spans="2:22">
-      <c r="C10" s="21"/>
-      <c r="D10" s="32"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="32"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="21"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
       <c r="L10" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M10" s="14"/>
       <c r="N10" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O10" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P10" s="14"/>
       <c r="Q10" s="5">
@@ -1296,32 +1296,32 @@
         <v>0</v>
       </c>
       <c r="R10" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S10" s="10"/>
       <c r="T10" s="10"/>
       <c r="U10" s="10"/>
     </row>
     <row r="11" spans="2:22">
-      <c r="C11" s="21"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="21"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
       <c r="L11" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M11" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N11" s="10"/>
       <c r="O11" s="10"/>
       <c r="P11" s="10"/>
       <c r="Q11" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="R11" s="10"/>
       <c r="S11" s="10"/>
@@ -1330,32 +1330,32 @@
     </row>
     <row r="12" spans="2:22">
       <c r="B12" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="E12" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="L12" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="M12" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="F12" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="21"/>
-      <c r="L12" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="M12" s="9" t="s">
-        <v>36</v>
-      </c>
       <c r="N12" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O12" s="9">
         <v>0</v>
@@ -1373,62 +1373,62 @@
       <c r="B13">
         <v>1</v>
       </c>
-      <c r="C13" s="21"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
       <c r="L13" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M13" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="N13" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="O13" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="P13" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="N13" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="O13" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="P13" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="11" t="s">
-        <v>38</v>
-      </c>
       <c r="R13" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S13" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T13" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U13" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="V13" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="2:22">
-      <c r="C14" s="21"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="21"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
       <c r="L14" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M14" s="13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N14" s="10"/>
       <c r="O14" s="10"/>
@@ -1436,36 +1436,36 @@
       <c r="Q14" s="10"/>
       <c r="R14" s="10"/>
       <c r="S14" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T14" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U14" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V14" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" spans="2:22">
-      <c r="C15" s="21"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="19"/>
       <c r="L15" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M15" s="14"/>
       <c r="N15" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O15" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P15" s="14"/>
       <c r="Q15" s="5">
@@ -1473,62 +1473,62 @@
         <v>192</v>
       </c>
       <c r="R15" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S15" s="10"/>
       <c r="T15" s="10"/>
       <c r="U15" s="10"/>
     </row>
     <row r="16" spans="2:22">
-      <c r="C16" s="21"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="21"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
       <c r="L16" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M16" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N16" s="10"/>
       <c r="O16" s="10"/>
       <c r="P16" s="10"/>
       <c r="Q16" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="S16" s="10"/>
       <c r="T16" s="10"/>
       <c r="U16" s="10"/>
     </row>
     <row r="17" spans="1:22">
-      <c r="C17" s="21" t="s">
+      <c r="C17" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" s="21"/>
+      <c r="E17" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="31"/>
-      <c r="E17" s="19" t="s">
+      <c r="F17" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="G17" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="19"/>
+      <c r="L17" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="M17" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F17" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="G17" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21"/>
-      <c r="J17" s="21"/>
-      <c r="L17" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="M17" s="9" t="s">
-        <v>36</v>
-      </c>
       <c r="N17" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O17" s="9">
         <v>0</v>
@@ -1543,62 +1543,62 @@
       <c r="U17" s="10"/>
     </row>
     <row r="18" spans="1:22">
-      <c r="C18" s="21"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="21"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
       <c r="L18" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M18" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="N18" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="O18" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="P18" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="N18" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="O18" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="P18" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="11" t="s">
-        <v>38</v>
-      </c>
       <c r="R18" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S18" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T18" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U18" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="V18" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:22">
-      <c r="C19" s="21"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="21"/>
-      <c r="I19" s="21"/>
-      <c r="J19" s="21"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="19"/>
       <c r="L19" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M19" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N19" s="10"/>
       <c r="O19" s="10"/>
@@ -1606,62 +1606,62 @@
       <c r="Q19" s="10"/>
       <c r="R19" s="10"/>
       <c r="S19" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T19" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U19" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V19" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:22">
-      <c r="C20" s="21"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="21"/>
-      <c r="I20" s="21"/>
-      <c r="J20" s="21"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="19"/>
       <c r="L20" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M20" s="14"/>
       <c r="N20" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O20" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P20" s="14"/>
       <c r="Q20" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R20" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S20" s="10"/>
       <c r="T20" s="10"/>
       <c r="U20" s="10"/>
     </row>
     <row r="21" spans="1:22">
-      <c r="C21" s="21"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="21"/>
-      <c r="J21" s="21"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="19"/>
       <c r="L21" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M21" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N21" s="10"/>
       <c r="O21" s="10"/>
@@ -1674,34 +1674,34 @@
     </row>
     <row r="22" spans="1:22">
       <c r="B22" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D22" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="E22" s="22"/>
-      <c r="F22" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="E22" s="25"/>
+      <c r="F22" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H22" s="19"/>
+      <c r="I22" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="J22" s="19"/>
+      <c r="L22" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="M22" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="G22" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="H22" s="21"/>
-      <c r="I22" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="J22" s="21"/>
-      <c r="L22" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="M22" s="9" t="s">
-        <v>36</v>
-      </c>
       <c r="N22" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O22" s="9">
         <v>0</v>
@@ -1719,62 +1719,62 @@
       <c r="B23">
         <v>2</v>
       </c>
-      <c r="C23" s="21"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="21"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="21"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="19"/>
       <c r="L23" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M23" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N23" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O23" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P23" s="11">
         <v>1</v>
       </c>
       <c r="Q23" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="R23" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="S23" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T23" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V23" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:22">
-      <c r="C24" s="21"/>
-      <c r="D24" s="32"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="21"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="21"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="24"/>
+      <c r="J24" s="19"/>
       <c r="L24" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M24" s="13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N24" s="10"/>
       <c r="O24" s="10"/>
@@ -1782,36 +1782,36 @@
       <c r="Q24" s="10"/>
       <c r="R24" s="10"/>
       <c r="S24" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T24" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U24" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="V24" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" spans="1:22">
-      <c r="C25" s="21"/>
-      <c r="D25" s="32"/>
-      <c r="E25" s="22"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="21"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="21"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="24"/>
+      <c r="J25" s="19"/>
       <c r="L25" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M25" s="14"/>
       <c r="N25" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O25" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P25" s="14"/>
       <c r="Q25" s="5">
@@ -1819,32 +1819,32 @@
         <v>384</v>
       </c>
       <c r="R25" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S25" s="10"/>
       <c r="T25" s="10"/>
       <c r="U25" s="10"/>
     </row>
     <row r="26" spans="1:22">
-      <c r="C26" s="21"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="21"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="21"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="24"/>
+      <c r="J26" s="19"/>
       <c r="L26" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M26" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N26" s="10"/>
       <c r="O26" s="10"/>
       <c r="P26" s="10"/>
       <c r="Q26" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="R26" s="10"/>
       <c r="S26" s="10"/>
@@ -1859,36 +1859,36 @@
     </row>
     <row r="29" spans="1:22">
       <c r="A29" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="D29" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="E29" s="25"/>
+      <c r="F29" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="G29" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="H29" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="I29" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="C29" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="D29" s="19" t="s">
+      <c r="J29" s="19"/>
+      <c r="L29" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="M29" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E29" s="22"/>
-      <c r="F29" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="G29" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="H29" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="I29" s="27" t="s">
+      <c r="N29" s="9" t="s">
         <v>46</v>
-      </c>
-      <c r="J29" s="21"/>
-      <c r="L29" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="M29" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="N29" s="9" t="s">
-        <v>47</v>
       </c>
       <c r="O29" s="9">
         <v>0</v>
@@ -1903,62 +1903,62 @@
       <c r="U29" s="10"/>
     </row>
     <row r="30" spans="1:22">
-      <c r="C30" s="21"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="22"/>
-      <c r="G30" s="21"/>
-      <c r="H30" s="20"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="24"/>
       <c r="I30" s="28"/>
-      <c r="J30" s="21"/>
+      <c r="J30" s="19"/>
       <c r="L30" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M30" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="N30" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="O30" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="P30" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="N30" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="O30" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="P30" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="11" t="s">
-        <v>38</v>
-      </c>
       <c r="R30" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S30" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T30" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="V30" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31" spans="1:22">
-      <c r="C31" s="21"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="21"/>
-      <c r="H31" s="20"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="24"/>
       <c r="I31" s="28"/>
-      <c r="J31" s="21"/>
+      <c r="J31" s="19"/>
       <c r="L31" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N31" s="10"/>
       <c r="O31" s="10"/>
@@ -1966,62 +1966,62 @@
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
       <c r="S31" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T31" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U31" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V31" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="32" spans="1:22">
-      <c r="C32" s="21"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="22"/>
-      <c r="F32" s="22"/>
-      <c r="G32" s="21"/>
-      <c r="H32" s="20"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="25"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="24"/>
       <c r="I32" s="28"/>
-      <c r="J32" s="21"/>
+      <c r="J32" s="19"/>
       <c r="L32" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M32" s="14"/>
       <c r="N32" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O32" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P32" s="14"/>
       <c r="Q32" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R32" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S32" s="10"/>
       <c r="T32" s="10"/>
       <c r="U32" s="10"/>
     </row>
     <row r="33" spans="2:22">
-      <c r="C33" s="21"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="22"/>
-      <c r="F33" s="22"/>
-      <c r="G33" s="21"/>
-      <c r="H33" s="20"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="24"/>
       <c r="I33" s="28"/>
-      <c r="J33" s="21"/>
+      <c r="J33" s="19"/>
       <c r="L33" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M33" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N33" s="10"/>
       <c r="O33" s="10"/>
@@ -2032,34 +2032,34 @@
       <c r="U33" s="10"/>
     </row>
     <row r="34" spans="2:22">
-      <c r="C34" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="D34" s="21"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="G34" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="H34" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="I34" s="19" t="s">
+      <c r="C34" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="G34" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="H34" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="I34" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="J34" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="L34" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="M34" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="J34" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="L34" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="M34" s="9" t="s">
-        <v>36</v>
-      </c>
       <c r="N34" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O34" s="9">
         <v>0</v>
@@ -2074,62 +2074,62 @@
       <c r="U34" s="10"/>
     </row>
     <row r="35" spans="2:22">
-      <c r="C35" s="21"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="22"/>
-      <c r="G35" s="21"/>
-      <c r="H35" s="21"/>
-      <c r="I35" s="19"/>
-      <c r="J35" s="20"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="19"/>
+      <c r="I35" s="20"/>
+      <c r="J35" s="24"/>
       <c r="L35" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M35" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N35" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O35" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P35" s="11">
         <v>0</v>
       </c>
       <c r="Q35" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="R35" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="R35" s="11" t="s">
-        <v>77</v>
-      </c>
       <c r="S35" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T35" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="V35" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36" spans="2:22">
-      <c r="C36" s="21"/>
-      <c r="D36" s="21"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="22"/>
-      <c r="G36" s="21"/>
-      <c r="H36" s="21"/>
-      <c r="I36" s="19"/>
-      <c r="J36" s="20"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="19"/>
+      <c r="F36" s="25"/>
+      <c r="G36" s="19"/>
+      <c r="H36" s="19"/>
+      <c r="I36" s="20"/>
+      <c r="J36" s="24"/>
       <c r="L36" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M36" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N36" s="10"/>
       <c r="O36" s="10"/>
@@ -2137,62 +2137,62 @@
       <c r="Q36" s="10"/>
       <c r="R36" s="10"/>
       <c r="S36" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T36" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U36" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V36" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37" spans="2:22">
-      <c r="C37" s="21"/>
-      <c r="D37" s="21"/>
-      <c r="E37" s="21"/>
-      <c r="F37" s="22"/>
-      <c r="G37" s="21"/>
-      <c r="H37" s="21"/>
-      <c r="I37" s="19"/>
-      <c r="J37" s="20"/>
+      <c r="C37" s="19"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="19"/>
+      <c r="H37" s="19"/>
+      <c r="I37" s="20"/>
+      <c r="J37" s="24"/>
       <c r="L37" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M37" s="14"/>
       <c r="N37" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O37" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P37" s="14"/>
       <c r="Q37" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R37" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S37" s="10"/>
       <c r="T37" s="10"/>
       <c r="U37" s="10"/>
     </row>
     <row r="38" spans="2:22">
-      <c r="C38" s="21"/>
-      <c r="D38" s="21"/>
-      <c r="E38" s="21"/>
-      <c r="F38" s="22"/>
-      <c r="G38" s="21"/>
-      <c r="H38" s="21"/>
-      <c r="I38" s="19"/>
-      <c r="J38" s="20"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="25"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="20"/>
+      <c r="J38" s="24"/>
       <c r="L38" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M38" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N38" s="10"/>
       <c r="O38" s="10"/>
@@ -2205,38 +2205,38 @@
     </row>
     <row r="39" spans="2:22">
       <c r="B39" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C39" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D39" s="21"/>
-      <c r="E39" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="F39" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C39" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="D39" s="19"/>
+      <c r="E39" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="F39" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G39" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H39" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I39" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="J39" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="L39" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="M39" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="G39" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="H39" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="I39" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="J39" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="L39" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="M39" s="9" t="s">
-        <v>36</v>
-      </c>
       <c r="N39" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O39" s="9">
         <v>0</v>
@@ -2254,65 +2254,65 @@
       <c r="B40">
         <v>3</v>
       </c>
-      <c r="C40" s="21"/>
-      <c r="D40" s="21"/>
-      <c r="E40" s="22"/>
-      <c r="F40" s="19"/>
-      <c r="G40" s="19"/>
-      <c r="H40" s="19"/>
-      <c r="I40" s="20"/>
-      <c r="J40" s="26"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="25"/>
+      <c r="F40" s="20"/>
+      <c r="G40" s="20"/>
+      <c r="H40" s="20"/>
+      <c r="I40" s="24"/>
+      <c r="J40" s="29"/>
       <c r="L40" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M40" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N40" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O40" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P40" s="11">
         <v>1</v>
       </c>
       <c r="Q40" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="R40" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="S40" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T40" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U40" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V40" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="41" spans="2:22">
       <c r="B41" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C41" s="21"/>
-      <c r="D41" s="21"/>
-      <c r="E41" s="22"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="19"/>
-      <c r="H41" s="19"/>
-      <c r="I41" s="20"/>
-      <c r="J41" s="26"/>
+        <v>51</v>
+      </c>
+      <c r="C41" s="19"/>
+      <c r="D41" s="19"/>
+      <c r="E41" s="25"/>
+      <c r="F41" s="20"/>
+      <c r="G41" s="20"/>
+      <c r="H41" s="20"/>
+      <c r="I41" s="24"/>
+      <c r="J41" s="29"/>
       <c r="L41" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M41" s="13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N41" s="10"/>
       <c r="O41" s="10"/>
@@ -2320,30 +2320,30 @@
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
       <c r="S41" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T41" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U41" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="V41" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="42" spans="2:22">
       <c r="B42">
         <v>0</v>
       </c>
-      <c r="C42" s="21"/>
-      <c r="D42" s="21"/>
-      <c r="E42" s="22"/>
-      <c r="F42" s="19"/>
-      <c r="G42" s="19"/>
-      <c r="H42" s="19"/>
-      <c r="I42" s="20"/>
-      <c r="J42" s="26"/>
+      <c r="C42" s="19"/>
+      <c r="D42" s="19"/>
+      <c r="E42" s="25"/>
+      <c r="F42" s="20"/>
+      <c r="G42" s="20"/>
+      <c r="H42" s="20"/>
+      <c r="I42" s="24"/>
+      <c r="J42" s="29"/>
       <c r="L42" s="14" t="s">
         <v>17</v>
       </c>
@@ -2353,7 +2353,7 @@
         <v>0</v>
       </c>
       <c r="O42" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P42" s="14"/>
       <c r="Q42" s="5">
@@ -2361,34 +2361,34 @@
         <v>576</v>
       </c>
       <c r="R42" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S42" s="10"/>
       <c r="T42" s="10"/>
       <c r="U42" s="10"/>
     </row>
     <row r="43" spans="2:22">
-      <c r="C43" s="21"/>
-      <c r="D43" s="21"/>
-      <c r="E43" s="22"/>
-      <c r="F43" s="19"/>
-      <c r="G43" s="19"/>
-      <c r="H43" s="19"/>
-      <c r="I43" s="20"/>
-      <c r="J43" s="26"/>
+      <c r="C43" s="19"/>
+      <c r="D43" s="19"/>
+      <c r="E43" s="25"/>
+      <c r="F43" s="20"/>
+      <c r="G43" s="20"/>
+      <c r="H43" s="20"/>
+      <c r="I43" s="24"/>
+      <c r="J43" s="29"/>
       <c r="L43" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M43" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O43" s="10"/>
       <c r="P43" s="10"/>
       <c r="Q43" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="R43" s="10"/>
       <c r="S43" s="10"/>
@@ -2399,34 +2399,34 @@
       <c r="P44" s="10"/>
     </row>
     <row r="45" spans="2:22">
-      <c r="C45" s="21" t="s">
+      <c r="C45" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="D45" s="20"/>
+      <c r="E45" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="D45" s="19"/>
-      <c r="E45" s="19" t="s">
+      <c r="F45" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G45" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="H45" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="I45" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="J45" s="19"/>
+      <c r="L45" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="M45" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F45" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="G45" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="H45" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="I45" s="27" t="s">
+      <c r="N45" s="9" t="s">
         <v>46</v>
-      </c>
-      <c r="J45" s="21"/>
-      <c r="L45" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="M45" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="N45" s="9" t="s">
-        <v>47</v>
       </c>
       <c r="O45" s="9">
         <v>0</v>
@@ -2441,62 +2441,62 @@
       <c r="U45" s="10"/>
     </row>
     <row r="46" spans="2:22">
-      <c r="C46" s="21"/>
-      <c r="D46" s="19"/>
-      <c r="E46" s="19"/>
-      <c r="F46" s="20"/>
-      <c r="G46" s="22"/>
-      <c r="H46" s="22"/>
+      <c r="C46" s="19"/>
+      <c r="D46" s="20"/>
+      <c r="E46" s="20"/>
+      <c r="F46" s="24"/>
+      <c r="G46" s="25"/>
+      <c r="H46" s="25"/>
       <c r="I46" s="28"/>
-      <c r="J46" s="21"/>
+      <c r="J46" s="19"/>
       <c r="L46" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M46" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="N46" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="O46" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="P46" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="N46" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="O46" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="P46" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="11" t="s">
-        <v>38</v>
-      </c>
       <c r="R46" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S46" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T46" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U46" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="V46" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="47" spans="2:22">
-      <c r="C47" s="21"/>
-      <c r="D47" s="19"/>
-      <c r="E47" s="19"/>
-      <c r="F47" s="20"/>
-      <c r="G47" s="22"/>
-      <c r="H47" s="22"/>
+      <c r="C47" s="19"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="24"/>
+      <c r="G47" s="25"/>
+      <c r="H47" s="25"/>
       <c r="I47" s="28"/>
-      <c r="J47" s="21"/>
+      <c r="J47" s="19"/>
       <c r="L47" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M47" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N47" s="10"/>
       <c r="O47" s="10"/>
@@ -2504,62 +2504,62 @@
       <c r="Q47" s="10"/>
       <c r="R47" s="10"/>
       <c r="S47" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T47" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U47" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V47" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="48" spans="2:22">
-      <c r="C48" s="21"/>
-      <c r="D48" s="19"/>
-      <c r="E48" s="19"/>
-      <c r="F48" s="20"/>
-      <c r="G48" s="22"/>
-      <c r="H48" s="22"/>
+      <c r="C48" s="19"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="20"/>
+      <c r="F48" s="24"/>
+      <c r="G48" s="25"/>
+      <c r="H48" s="25"/>
       <c r="I48" s="28"/>
-      <c r="J48" s="21"/>
+      <c r="J48" s="19"/>
       <c r="L48" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M48" s="14"/>
       <c r="N48" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O48" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P48" s="14"/>
       <c r="Q48" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R48" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S48" s="10"/>
       <c r="T48" s="10"/>
       <c r="U48" s="10"/>
     </row>
     <row r="49" spans="2:22">
-      <c r="C49" s="21"/>
-      <c r="D49" s="19"/>
-      <c r="E49" s="19"/>
-      <c r="F49" s="20"/>
-      <c r="G49" s="22"/>
-      <c r="H49" s="22"/>
+      <c r="C49" s="19"/>
+      <c r="D49" s="20"/>
+      <c r="E49" s="20"/>
+      <c r="F49" s="24"/>
+      <c r="G49" s="25"/>
+      <c r="H49" s="25"/>
       <c r="I49" s="28"/>
-      <c r="J49" s="21"/>
+      <c r="J49" s="19"/>
       <c r="L49" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M49" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N49" s="10"/>
       <c r="O49" s="10"/>
@@ -2570,34 +2570,34 @@
       <c r="U49" s="10"/>
     </row>
     <row r="50" spans="2:22">
-      <c r="C50" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="D50" s="21"/>
-      <c r="E50" s="21"/>
-      <c r="F50" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="G50" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="H50" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="I50" s="19" t="s">
+      <c r="C50" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D50" s="19"/>
+      <c r="E50" s="19"/>
+      <c r="F50" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="G50" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="H50" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="I50" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="J50" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="L50" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="M50" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="J50" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="L50" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="M50" s="9" t="s">
-        <v>36</v>
-      </c>
       <c r="N50" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O50" s="9">
         <v>0</v>
@@ -2612,62 +2612,62 @@
       <c r="U50" s="10"/>
     </row>
     <row r="51" spans="2:22">
-      <c r="C51" s="21"/>
-      <c r="D51" s="21"/>
-      <c r="E51" s="21"/>
-      <c r="F51" s="24"/>
-      <c r="G51" s="24"/>
-      <c r="H51" s="24"/>
-      <c r="I51" s="19"/>
-      <c r="J51" s="20"/>
+      <c r="C51" s="19"/>
+      <c r="D51" s="19"/>
+      <c r="E51" s="19"/>
+      <c r="F51" s="31"/>
+      <c r="G51" s="31"/>
+      <c r="H51" s="31"/>
+      <c r="I51" s="20"/>
+      <c r="J51" s="24"/>
       <c r="L51" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M51" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N51" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O51" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P51" s="11">
         <v>0</v>
       </c>
       <c r="Q51" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="R51" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="R51" s="11" t="s">
-        <v>77</v>
-      </c>
       <c r="S51" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T51" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U51" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="V51" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="52" spans="2:22">
-      <c r="C52" s="21"/>
-      <c r="D52" s="21"/>
-      <c r="E52" s="21"/>
-      <c r="F52" s="24"/>
-      <c r="G52" s="24"/>
-      <c r="H52" s="24"/>
-      <c r="I52" s="19"/>
-      <c r="J52" s="20"/>
+      <c r="C52" s="19"/>
+      <c r="D52" s="19"/>
+      <c r="E52" s="19"/>
+      <c r="F52" s="31"/>
+      <c r="G52" s="31"/>
+      <c r="H52" s="31"/>
+      <c r="I52" s="20"/>
+      <c r="J52" s="24"/>
       <c r="L52" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M52" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N52" s="10"/>
       <c r="O52" s="10"/>
@@ -2675,62 +2675,62 @@
       <c r="Q52" s="10"/>
       <c r="R52" s="10"/>
       <c r="S52" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T52" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U52" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V52" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="53" spans="2:22">
-      <c r="C53" s="21"/>
-      <c r="D53" s="21"/>
-      <c r="E53" s="21"/>
-      <c r="F53" s="24"/>
-      <c r="G53" s="24"/>
-      <c r="H53" s="24"/>
-      <c r="I53" s="19"/>
-      <c r="J53" s="20"/>
+      <c r="C53" s="19"/>
+      <c r="D53" s="19"/>
+      <c r="E53" s="19"/>
+      <c r="F53" s="31"/>
+      <c r="G53" s="31"/>
+      <c r="H53" s="31"/>
+      <c r="I53" s="20"/>
+      <c r="J53" s="24"/>
       <c r="L53" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M53" s="14"/>
       <c r="N53" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O53" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P53" s="14"/>
       <c r="Q53" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R53" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S53" s="10"/>
       <c r="T53" s="10"/>
       <c r="U53" s="10"/>
     </row>
     <row r="54" spans="2:22">
-      <c r="C54" s="21"/>
-      <c r="D54" s="21"/>
-      <c r="E54" s="21"/>
-      <c r="F54" s="25"/>
-      <c r="G54" s="25"/>
-      <c r="H54" s="25"/>
-      <c r="I54" s="19"/>
-      <c r="J54" s="20"/>
+      <c r="C54" s="19"/>
+      <c r="D54" s="19"/>
+      <c r="E54" s="19"/>
+      <c r="F54" s="32"/>
+      <c r="G54" s="32"/>
+      <c r="H54" s="32"/>
+      <c r="I54" s="20"/>
+      <c r="J54" s="24"/>
       <c r="L54" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M54" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N54" s="10"/>
       <c r="O54" s="10"/>
@@ -2743,38 +2743,38 @@
     </row>
     <row r="55" spans="2:22">
       <c r="B55" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C55" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D55" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="E55" s="22"/>
-      <c r="F55" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C55" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="D55" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="E55" s="25"/>
+      <c r="F55" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G55" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H55" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I55" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="J55" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="L55" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="M55" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="G55" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="H55" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="I55" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="J55" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="L55" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="M55" s="9" t="s">
-        <v>36</v>
-      </c>
       <c r="N55" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O55" s="9">
         <v>0</v>
@@ -2792,65 +2792,65 @@
       <c r="B56">
         <v>4</v>
       </c>
-      <c r="C56" s="21"/>
-      <c r="D56" s="22"/>
-      <c r="E56" s="22"/>
-      <c r="F56" s="19"/>
-      <c r="G56" s="19"/>
-      <c r="H56" s="19"/>
-      <c r="I56" s="20"/>
-      <c r="J56" s="26"/>
+      <c r="C56" s="19"/>
+      <c r="D56" s="25"/>
+      <c r="E56" s="25"/>
+      <c r="F56" s="20"/>
+      <c r="G56" s="20"/>
+      <c r="H56" s="20"/>
+      <c r="I56" s="24"/>
+      <c r="J56" s="29"/>
       <c r="L56" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M56" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N56" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O56" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P56" s="11">
         <v>1</v>
       </c>
       <c r="Q56" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="R56" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="S56" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T56" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U56" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V56" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="57" spans="2:22">
       <c r="B57" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C57" s="21"/>
-      <c r="D57" s="22"/>
-      <c r="E57" s="22"/>
-      <c r="F57" s="19"/>
-      <c r="G57" s="19"/>
-      <c r="H57" s="19"/>
-      <c r="I57" s="20"/>
-      <c r="J57" s="26"/>
+        <v>51</v>
+      </c>
+      <c r="C57" s="19"/>
+      <c r="D57" s="25"/>
+      <c r="E57" s="25"/>
+      <c r="F57" s="20"/>
+      <c r="G57" s="20"/>
+      <c r="H57" s="20"/>
+      <c r="I57" s="24"/>
+      <c r="J57" s="29"/>
       <c r="L57" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M57" s="13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N57" s="10"/>
       <c r="O57" s="10"/>
@@ -2858,30 +2858,30 @@
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
       <c r="S57" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T57" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U57" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="V57" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="58" spans="2:22">
       <c r="B58">
         <v>1</v>
       </c>
-      <c r="C58" s="21"/>
-      <c r="D58" s="22"/>
-      <c r="E58" s="22"/>
-      <c r="F58" s="19"/>
-      <c r="G58" s="19"/>
-      <c r="H58" s="19"/>
-      <c r="I58" s="20"/>
-      <c r="J58" s="26"/>
+      <c r="C58" s="19"/>
+      <c r="D58" s="25"/>
+      <c r="E58" s="25"/>
+      <c r="F58" s="20"/>
+      <c r="G58" s="20"/>
+      <c r="H58" s="20"/>
+      <c r="I58" s="24"/>
+      <c r="J58" s="29"/>
       <c r="L58" s="14" t="s">
         <v>17</v>
       </c>
@@ -2891,7 +2891,7 @@
         <v>192</v>
       </c>
       <c r="O58" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P58" s="14"/>
       <c r="Q58" s="5">
@@ -2899,34 +2899,34 @@
         <v>768</v>
       </c>
       <c r="R58" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S58" s="10"/>
       <c r="T58" s="10"/>
       <c r="U58" s="10"/>
     </row>
     <row r="59" spans="2:22">
-      <c r="C59" s="21"/>
-      <c r="D59" s="22"/>
-      <c r="E59" s="22"/>
-      <c r="F59" s="19"/>
-      <c r="G59" s="19"/>
-      <c r="H59" s="19"/>
-      <c r="I59" s="20"/>
-      <c r="J59" s="26"/>
+      <c r="C59" s="19"/>
+      <c r="D59" s="25"/>
+      <c r="E59" s="25"/>
+      <c r="F59" s="20"/>
+      <c r="G59" s="20"/>
+      <c r="H59" s="20"/>
+      <c r="I59" s="24"/>
+      <c r="J59" s="29"/>
       <c r="L59" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M59" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O59" s="10"/>
       <c r="P59" s="10"/>
       <c r="Q59" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R59" s="10"/>
       <c r="S59" s="10"/>
@@ -2937,34 +2937,34 @@
       <c r="P60" s="10"/>
     </row>
     <row r="61" spans="2:22">
-      <c r="C61" s="21" t="s">
+      <c r="C61" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="D61" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="D61" s="19" t="s">
+      <c r="E61" s="25"/>
+      <c r="F61" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="G61" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="H61" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="I61" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="J61" s="19"/>
+      <c r="L61" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="M61" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E61" s="22"/>
-      <c r="F61" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="G61" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="H61" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="I61" s="27" t="s">
+      <c r="N61" s="9" t="s">
         <v>46</v>
-      </c>
-      <c r="J61" s="21"/>
-      <c r="L61" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="M61" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="N61" s="9" t="s">
-        <v>47</v>
       </c>
       <c r="O61" s="9">
         <v>0</v>
@@ -2979,62 +2979,62 @@
       <c r="U61" s="10"/>
     </row>
     <row r="62" spans="2:22">
-      <c r="C62" s="21"/>
-      <c r="D62" s="19"/>
-      <c r="E62" s="22"/>
-      <c r="F62" s="21"/>
-      <c r="G62" s="20"/>
-      <c r="H62" s="21"/>
+      <c r="C62" s="19"/>
+      <c r="D62" s="20"/>
+      <c r="E62" s="25"/>
+      <c r="F62" s="19"/>
+      <c r="G62" s="24"/>
+      <c r="H62" s="19"/>
       <c r="I62" s="28"/>
-      <c r="J62" s="21"/>
+      <c r="J62" s="19"/>
       <c r="L62" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M62" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="N62" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="O62" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="P62" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="N62" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="O62" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="P62" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="11" t="s">
-        <v>38</v>
-      </c>
       <c r="R62" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S62" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T62" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U62" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="V62" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="63" spans="2:22">
-      <c r="C63" s="21"/>
-      <c r="D63" s="19"/>
-      <c r="E63" s="22"/>
-      <c r="F63" s="21"/>
-      <c r="G63" s="20"/>
-      <c r="H63" s="21"/>
+      <c r="C63" s="19"/>
+      <c r="D63" s="20"/>
+      <c r="E63" s="25"/>
+      <c r="F63" s="19"/>
+      <c r="G63" s="24"/>
+      <c r="H63" s="19"/>
       <c r="I63" s="28"/>
-      <c r="J63" s="21"/>
+      <c r="J63" s="19"/>
       <c r="L63" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M63" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N63" s="10"/>
       <c r="O63" s="10"/>
@@ -3042,62 +3042,62 @@
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
       <c r="S63" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T63" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U63" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V63" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="64" spans="2:22">
-      <c r="C64" s="21"/>
-      <c r="D64" s="19"/>
-      <c r="E64" s="22"/>
-      <c r="F64" s="21"/>
-      <c r="G64" s="20"/>
-      <c r="H64" s="21"/>
+      <c r="C64" s="19"/>
+      <c r="D64" s="20"/>
+      <c r="E64" s="25"/>
+      <c r="F64" s="19"/>
+      <c r="G64" s="24"/>
+      <c r="H64" s="19"/>
       <c r="I64" s="28"/>
-      <c r="J64" s="21"/>
+      <c r="J64" s="19"/>
       <c r="L64" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M64" s="14"/>
       <c r="N64" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O64" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P64" s="14"/>
       <c r="Q64" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R64" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S64" s="10"/>
       <c r="T64" s="10"/>
       <c r="U64" s="10"/>
     </row>
     <row r="65" spans="2:22">
-      <c r="C65" s="21"/>
-      <c r="D65" s="19"/>
-      <c r="E65" s="22"/>
-      <c r="F65" s="21"/>
-      <c r="G65" s="20"/>
-      <c r="H65" s="21"/>
+      <c r="C65" s="19"/>
+      <c r="D65" s="20"/>
+      <c r="E65" s="25"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="24"/>
+      <c r="H65" s="19"/>
       <c r="I65" s="28"/>
-      <c r="J65" s="21"/>
+      <c r="J65" s="19"/>
       <c r="L65" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M65" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N65" s="10"/>
       <c r="O65" s="10"/>
@@ -3108,34 +3108,34 @@
       <c r="U65" s="10"/>
     </row>
     <row r="66" spans="2:22">
-      <c r="C66" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="D66" s="21"/>
-      <c r="E66" s="21"/>
-      <c r="F66" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="G66" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="H66" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="I66" s="19" t="s">
+      <c r="C66" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D66" s="19"/>
+      <c r="E66" s="19"/>
+      <c r="F66" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="G66" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="H66" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="I66" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="J66" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="L66" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="M66" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="J66" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="L66" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="M66" s="9" t="s">
-        <v>36</v>
-      </c>
       <c r="N66" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O66" s="9">
         <v>0</v>
@@ -3150,62 +3150,62 @@
       <c r="U66" s="10"/>
     </row>
     <row r="67" spans="2:22">
-      <c r="C67" s="21"/>
-      <c r="D67" s="21"/>
-      <c r="E67" s="21"/>
-      <c r="F67" s="21"/>
-      <c r="G67" s="21"/>
-      <c r="H67" s="21"/>
-      <c r="I67" s="19"/>
-      <c r="J67" s="20"/>
+      <c r="C67" s="19"/>
+      <c r="D67" s="19"/>
+      <c r="E67" s="19"/>
+      <c r="F67" s="19"/>
+      <c r="G67" s="19"/>
+      <c r="H67" s="19"/>
+      <c r="I67" s="20"/>
+      <c r="J67" s="24"/>
       <c r="L67" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M67" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N67" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O67" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P67" s="11">
         <v>0</v>
       </c>
       <c r="Q67" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="R67" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="R67" s="11" t="s">
-        <v>77</v>
-      </c>
       <c r="S67" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T67" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U67" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="V67" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="68" spans="2:22">
-      <c r="C68" s="21"/>
-      <c r="D68" s="21"/>
-      <c r="E68" s="21"/>
-      <c r="F68" s="21"/>
-      <c r="G68" s="21"/>
-      <c r="H68" s="21"/>
-      <c r="I68" s="19"/>
-      <c r="J68" s="20"/>
+      <c r="C68" s="19"/>
+      <c r="D68" s="19"/>
+      <c r="E68" s="19"/>
+      <c r="F68" s="19"/>
+      <c r="G68" s="19"/>
+      <c r="H68" s="19"/>
+      <c r="I68" s="20"/>
+      <c r="J68" s="24"/>
       <c r="L68" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M68" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N68" s="10"/>
       <c r="O68" s="10"/>
@@ -3213,62 +3213,62 @@
       <c r="Q68" s="10"/>
       <c r="R68" s="10"/>
       <c r="S68" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T68" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U68" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V68" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="69" spans="2:22">
-      <c r="C69" s="21"/>
-      <c r="D69" s="21"/>
-      <c r="E69" s="21"/>
-      <c r="F69" s="21"/>
-      <c r="G69" s="21"/>
-      <c r="H69" s="21"/>
-      <c r="I69" s="19"/>
-      <c r="J69" s="20"/>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="20"/>
+      <c r="J69" s="24"/>
       <c r="L69" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M69" s="14"/>
       <c r="N69" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O69" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P69" s="14"/>
       <c r="Q69" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R69" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S69" s="10"/>
       <c r="T69" s="10"/>
       <c r="U69" s="10"/>
     </row>
     <row r="70" spans="2:22">
-      <c r="C70" s="21"/>
-      <c r="D70" s="21"/>
-      <c r="E70" s="21"/>
-      <c r="F70" s="21"/>
-      <c r="G70" s="21"/>
-      <c r="H70" s="21"/>
-      <c r="I70" s="19"/>
-      <c r="J70" s="20"/>
+      <c r="C70" s="19"/>
+      <c r="D70" s="19"/>
+      <c r="E70" s="19"/>
+      <c r="F70" s="19"/>
+      <c r="G70" s="19"/>
+      <c r="H70" s="19"/>
+      <c r="I70" s="20"/>
+      <c r="J70" s="24"/>
       <c r="L70" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M70" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N70" s="10"/>
       <c r="O70" s="10"/>
@@ -3281,38 +3281,38 @@
     </row>
     <row r="71" spans="2:22">
       <c r="B71" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C71" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D71" s="21"/>
-      <c r="E71" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="F71" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C71" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="D71" s="19"/>
+      <c r="E71" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="F71" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G71" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H71" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I71" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="J71" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="L71" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="M71" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="G71" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="H71" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="I71" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="J71" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="L71" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="M71" s="9" t="s">
-        <v>36</v>
-      </c>
       <c r="N71" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O71" s="9">
         <v>0</v>
@@ -3330,65 +3330,65 @@
       <c r="B72">
         <v>5</v>
       </c>
-      <c r="C72" s="21"/>
-      <c r="D72" s="21"/>
-      <c r="E72" s="22"/>
-      <c r="F72" s="19"/>
-      <c r="G72" s="19"/>
-      <c r="H72" s="19"/>
-      <c r="I72" s="20"/>
-      <c r="J72" s="26"/>
+      <c r="C72" s="19"/>
+      <c r="D72" s="19"/>
+      <c r="E72" s="25"/>
+      <c r="F72" s="20"/>
+      <c r="G72" s="20"/>
+      <c r="H72" s="20"/>
+      <c r="I72" s="24"/>
+      <c r="J72" s="29"/>
       <c r="L72" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M72" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N72" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O72" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P72" s="11">
         <v>1</v>
       </c>
       <c r="Q72" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="R72" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="S72" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T72" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U72" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V72" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="73" spans="2:22">
       <c r="B73" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C73" s="21"/>
-      <c r="D73" s="21"/>
-      <c r="E73" s="22"/>
-      <c r="F73" s="19"/>
-      <c r="G73" s="19"/>
-      <c r="H73" s="19"/>
-      <c r="I73" s="20"/>
-      <c r="J73" s="26"/>
+        <v>51</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="25"/>
+      <c r="F73" s="20"/>
+      <c r="G73" s="20"/>
+      <c r="H73" s="20"/>
+      <c r="I73" s="24"/>
+      <c r="J73" s="29"/>
       <c r="L73" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M73" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N73" s="10"/>
       <c r="O73" s="10"/>
@@ -3396,30 +3396,30 @@
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
       <c r="S73" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T73" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U73" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="V73" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="74" spans="2:22">
       <c r="B74">
         <v>2</v>
       </c>
-      <c r="C74" s="21"/>
-      <c r="D74" s="21"/>
-      <c r="E74" s="22"/>
-      <c r="F74" s="19"/>
-      <c r="G74" s="19"/>
-      <c r="H74" s="19"/>
-      <c r="I74" s="20"/>
-      <c r="J74" s="26"/>
+      <c r="C74" s="19"/>
+      <c r="D74" s="19"/>
+      <c r="E74" s="25"/>
+      <c r="F74" s="20"/>
+      <c r="G74" s="20"/>
+      <c r="H74" s="20"/>
+      <c r="I74" s="24"/>
+      <c r="J74" s="29"/>
       <c r="L74" s="14" t="s">
         <v>17</v>
       </c>
@@ -3429,7 +3429,7 @@
         <v>384</v>
       </c>
       <c r="O74" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P74" s="14"/>
       <c r="Q74" s="5">
@@ -3437,34 +3437,34 @@
         <v>960</v>
       </c>
       <c r="R74" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S74" s="10"/>
       <c r="T74" s="10"/>
       <c r="U74" s="10"/>
     </row>
     <row r="75" spans="2:22">
-      <c r="C75" s="21"/>
-      <c r="D75" s="21"/>
-      <c r="E75" s="22"/>
-      <c r="F75" s="19"/>
-      <c r="G75" s="19"/>
-      <c r="H75" s="19"/>
-      <c r="I75" s="20"/>
-      <c r="J75" s="26"/>
+      <c r="C75" s="19"/>
+      <c r="D75" s="19"/>
+      <c r="E75" s="25"/>
+      <c r="F75" s="20"/>
+      <c r="G75" s="20"/>
+      <c r="H75" s="20"/>
+      <c r="I75" s="24"/>
+      <c r="J75" s="29"/>
       <c r="L75" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M75" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="O75" s="10"/>
       <c r="P75" s="10"/>
       <c r="Q75" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="R75" s="10"/>
       <c r="S75" s="10"/>
@@ -3475,34 +3475,34 @@
       <c r="P76" s="10"/>
     </row>
     <row r="77" spans="2:22">
-      <c r="C77" s="21" t="s">
+      <c r="C77" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="D77" s="20"/>
+      <c r="E77" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="D77" s="19"/>
-      <c r="E77" s="19" t="s">
+      <c r="F77" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="G77" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="H77" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="I77" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="J77" s="19"/>
+      <c r="L77" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="M77" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F77" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="G77" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="H77" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="I77" s="27" t="s">
+      <c r="N77" s="9" t="s">
         <v>46</v>
-      </c>
-      <c r="J77" s="21"/>
-      <c r="L77" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="M77" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="N77" s="9" t="s">
-        <v>47</v>
       </c>
       <c r="O77" s="9">
         <v>0</v>
@@ -3517,62 +3517,62 @@
       <c r="U77" s="10"/>
     </row>
     <row r="78" spans="2:22">
-      <c r="C78" s="21"/>
-      <c r="D78" s="19"/>
-      <c r="E78" s="19"/>
-      <c r="F78" s="21"/>
-      <c r="G78" s="21"/>
-      <c r="H78" s="20"/>
+      <c r="C78" s="19"/>
+      <c r="D78" s="20"/>
+      <c r="E78" s="20"/>
+      <c r="F78" s="19"/>
+      <c r="G78" s="19"/>
+      <c r="H78" s="24"/>
       <c r="I78" s="28"/>
-      <c r="J78" s="21"/>
+      <c r="J78" s="19"/>
       <c r="L78" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M78" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="N78" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="O78" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="P78" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="N78" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="O78" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="P78" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q78" s="11" t="s">
-        <v>38</v>
-      </c>
       <c r="R78" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S78" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T78" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U78" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="V78" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="79" spans="2:22">
-      <c r="C79" s="21"/>
-      <c r="D79" s="19"/>
-      <c r="E79" s="19"/>
-      <c r="F79" s="21"/>
-      <c r="G79" s="21"/>
-      <c r="H79" s="20"/>
+      <c r="C79" s="19"/>
+      <c r="D79" s="20"/>
+      <c r="E79" s="20"/>
+      <c r="F79" s="19"/>
+      <c r="G79" s="19"/>
+      <c r="H79" s="24"/>
       <c r="I79" s="28"/>
-      <c r="J79" s="21"/>
+      <c r="J79" s="19"/>
       <c r="L79" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M79" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N79" s="10"/>
       <c r="O79" s="10"/>
@@ -3580,62 +3580,62 @@
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
       <c r="S79" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T79" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U79" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V79" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="80" spans="2:22">
-      <c r="C80" s="21"/>
-      <c r="D80" s="19"/>
-      <c r="E80" s="19"/>
-      <c r="F80" s="21"/>
-      <c r="G80" s="21"/>
-      <c r="H80" s="20"/>
+      <c r="C80" s="19"/>
+      <c r="D80" s="20"/>
+      <c r="E80" s="20"/>
+      <c r="F80" s="19"/>
+      <c r="G80" s="19"/>
+      <c r="H80" s="24"/>
       <c r="I80" s="28"/>
-      <c r="J80" s="21"/>
+      <c r="J80" s="19"/>
       <c r="L80" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M80" s="14"/>
       <c r="N80" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O80" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P80" s="14"/>
       <c r="Q80" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R80" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S80" s="10"/>
       <c r="T80" s="10"/>
       <c r="U80" s="10"/>
     </row>
     <row r="81" spans="2:22">
-      <c r="C81" s="21"/>
-      <c r="D81" s="19"/>
-      <c r="E81" s="19"/>
-      <c r="F81" s="21"/>
-      <c r="G81" s="21"/>
-      <c r="H81" s="20"/>
+      <c r="C81" s="19"/>
+      <c r="D81" s="20"/>
+      <c r="E81" s="20"/>
+      <c r="F81" s="19"/>
+      <c r="G81" s="19"/>
+      <c r="H81" s="24"/>
       <c r="I81" s="28"/>
-      <c r="J81" s="21"/>
+      <c r="J81" s="19"/>
       <c r="L81" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M81" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N81" s="10"/>
       <c r="O81" s="10"/>
@@ -3646,34 +3646,34 @@
       <c r="U81" s="10"/>
     </row>
     <row r="82" spans="2:22">
-      <c r="C82" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="D82" s="21"/>
-      <c r="E82" s="21"/>
-      <c r="F82" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="G82" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="H82" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="I82" s="19" t="s">
+      <c r="C82" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D82" s="19"/>
+      <c r="E82" s="19"/>
+      <c r="F82" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="G82" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="H82" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="I82" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="J82" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="L82" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="M82" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="J82" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="L82" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="M82" s="9" t="s">
-        <v>36</v>
-      </c>
       <c r="N82" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O82" s="9">
         <v>0</v>
@@ -3688,62 +3688,62 @@
       <c r="U82" s="10"/>
     </row>
     <row r="83" spans="2:22">
-      <c r="C83" s="21"/>
-      <c r="D83" s="21"/>
-      <c r="E83" s="21"/>
-      <c r="F83" s="21"/>
-      <c r="G83" s="21"/>
-      <c r="H83" s="21"/>
-      <c r="I83" s="19"/>
-      <c r="J83" s="20"/>
+      <c r="C83" s="19"/>
+      <c r="D83" s="19"/>
+      <c r="E83" s="19"/>
+      <c r="F83" s="19"/>
+      <c r="G83" s="19"/>
+      <c r="H83" s="19"/>
+      <c r="I83" s="20"/>
+      <c r="J83" s="24"/>
       <c r="L83" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M83" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N83" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O83" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P83" s="11">
         <v>0</v>
       </c>
       <c r="Q83" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="R83" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="R83" s="11" t="s">
-        <v>77</v>
-      </c>
       <c r="S83" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T83" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U83" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="V83" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="84" spans="2:22">
-      <c r="C84" s="21"/>
-      <c r="D84" s="21"/>
-      <c r="E84" s="21"/>
-      <c r="F84" s="21"/>
-      <c r="G84" s="21"/>
-      <c r="H84" s="21"/>
-      <c r="I84" s="19"/>
-      <c r="J84" s="20"/>
+      <c r="C84" s="19"/>
+      <c r="D84" s="19"/>
+      <c r="E84" s="19"/>
+      <c r="F84" s="19"/>
+      <c r="G84" s="19"/>
+      <c r="H84" s="19"/>
+      <c r="I84" s="20"/>
+      <c r="J84" s="24"/>
       <c r="L84" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M84" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N84" s="10"/>
       <c r="O84" s="10"/>
@@ -3751,62 +3751,62 @@
       <c r="Q84" s="10"/>
       <c r="R84" s="10"/>
       <c r="S84" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T84" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U84" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V84" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="85" spans="2:22">
-      <c r="C85" s="21"/>
-      <c r="D85" s="21"/>
-      <c r="E85" s="21"/>
-      <c r="F85" s="21"/>
-      <c r="G85" s="21"/>
-      <c r="H85" s="21"/>
-      <c r="I85" s="19"/>
-      <c r="J85" s="20"/>
+      <c r="C85" s="19"/>
+      <c r="D85" s="19"/>
+      <c r="E85" s="19"/>
+      <c r="F85" s="19"/>
+      <c r="G85" s="19"/>
+      <c r="H85" s="19"/>
+      <c r="I85" s="20"/>
+      <c r="J85" s="24"/>
       <c r="L85" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M85" s="14"/>
       <c r="N85" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O85" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P85" s="14"/>
       <c r="Q85" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R85" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S85" s="10"/>
       <c r="T85" s="10"/>
       <c r="U85" s="10"/>
     </row>
     <row r="86" spans="2:22">
-      <c r="C86" s="21"/>
-      <c r="D86" s="21"/>
-      <c r="E86" s="21"/>
-      <c r="F86" s="21"/>
-      <c r="G86" s="21"/>
-      <c r="H86" s="21"/>
-      <c r="I86" s="19"/>
-      <c r="J86" s="20"/>
+      <c r="C86" s="19"/>
+      <c r="D86" s="19"/>
+      <c r="E86" s="19"/>
+      <c r="F86" s="19"/>
+      <c r="G86" s="19"/>
+      <c r="H86" s="19"/>
+      <c r="I86" s="20"/>
+      <c r="J86" s="24"/>
       <c r="L86" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M86" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N86" s="10"/>
       <c r="O86" s="10"/>
@@ -3819,38 +3819,38 @@
     </row>
     <row r="87" spans="2:22">
       <c r="B87" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C87" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D87" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="E87" s="22"/>
-      <c r="F87" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C87" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="D87" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="E87" s="25"/>
+      <c r="F87" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G87" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H87" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I87" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="J87" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="L87" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="M87" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="G87" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="H87" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="I87" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="J87" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="L87" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="M87" s="9" t="s">
-        <v>36</v>
-      </c>
       <c r="N87" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O87" s="9">
         <v>0</v>
@@ -3868,65 +3868,65 @@
       <c r="B88">
         <v>6</v>
       </c>
-      <c r="C88" s="21"/>
-      <c r="D88" s="22"/>
-      <c r="E88" s="22"/>
-      <c r="F88" s="19"/>
-      <c r="G88" s="19"/>
-      <c r="H88" s="19"/>
-      <c r="I88" s="20"/>
-      <c r="J88" s="26"/>
+      <c r="C88" s="19"/>
+      <c r="D88" s="25"/>
+      <c r="E88" s="25"/>
+      <c r="F88" s="20"/>
+      <c r="G88" s="20"/>
+      <c r="H88" s="20"/>
+      <c r="I88" s="24"/>
+      <c r="J88" s="29"/>
       <c r="L88" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M88" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N88" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O88" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P88" s="11">
         <v>1</v>
       </c>
       <c r="Q88" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="R88" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="S88" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T88" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U88" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V88" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="89" spans="2:22">
       <c r="B89" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C89" s="21"/>
-      <c r="D89" s="22"/>
-      <c r="E89" s="22"/>
-      <c r="F89" s="19"/>
-      <c r="G89" s="19"/>
-      <c r="H89" s="19"/>
-      <c r="I89" s="20"/>
-      <c r="J89" s="26"/>
+        <v>51</v>
+      </c>
+      <c r="C89" s="19"/>
+      <c r="D89" s="25"/>
+      <c r="E89" s="25"/>
+      <c r="F89" s="20"/>
+      <c r="G89" s="20"/>
+      <c r="H89" s="20"/>
+      <c r="I89" s="24"/>
+      <c r="J89" s="29"/>
       <c r="L89" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M89" s="13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N89" s="10"/>
       <c r="O89" s="10"/>
@@ -3934,30 +3934,30 @@
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
       <c r="S89" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T89" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U89" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="V89" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="90" spans="2:22">
       <c r="B90">
         <v>3</v>
       </c>
-      <c r="C90" s="21"/>
-      <c r="D90" s="22"/>
-      <c r="E90" s="22"/>
-      <c r="F90" s="19"/>
-      <c r="G90" s="19"/>
-      <c r="H90" s="19"/>
-      <c r="I90" s="20"/>
-      <c r="J90" s="26"/>
+      <c r="C90" s="19"/>
+      <c r="D90" s="25"/>
+      <c r="E90" s="25"/>
+      <c r="F90" s="20"/>
+      <c r="G90" s="20"/>
+      <c r="H90" s="20"/>
+      <c r="I90" s="24"/>
+      <c r="J90" s="29"/>
       <c r="L90" s="14" t="s">
         <v>17</v>
       </c>
@@ -3967,7 +3967,7 @@
         <v>576</v>
       </c>
       <c r="O90" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P90" s="14"/>
       <c r="Q90" s="5">
@@ -3975,34 +3975,34 @@
         <v>1152</v>
       </c>
       <c r="R90" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S90" s="10"/>
       <c r="T90" s="10"/>
       <c r="U90" s="10"/>
     </row>
     <row r="91" spans="2:22">
-      <c r="C91" s="21"/>
-      <c r="D91" s="22"/>
-      <c r="E91" s="22"/>
-      <c r="F91" s="19"/>
-      <c r="G91" s="19"/>
-      <c r="H91" s="19"/>
-      <c r="I91" s="20"/>
-      <c r="J91" s="26"/>
+      <c r="C91" s="19"/>
+      <c r="D91" s="25"/>
+      <c r="E91" s="25"/>
+      <c r="F91" s="20"/>
+      <c r="G91" s="20"/>
+      <c r="H91" s="20"/>
+      <c r="I91" s="24"/>
+      <c r="J91" s="29"/>
       <c r="L91" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M91" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O91" s="10"/>
       <c r="P91" s="10"/>
       <c r="Q91" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="R91" s="10"/>
       <c r="S91" s="10"/>
@@ -4016,41 +4016,41 @@
       <c r="P93" s="10"/>
     </row>
     <row r="94" spans="2:22">
-      <c r="B94" s="29" t="s">
-        <v>65</v>
-      </c>
-      <c r="C94" s="29"/>
+      <c r="B94" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="C94" s="33"/>
       <c r="P94" s="10"/>
     </row>
     <row r="95" spans="2:22">
-      <c r="C95" s="21" t="s">
+      <c r="C95" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="D95" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="D95" s="19" t="s">
+      <c r="E95" s="25"/>
+      <c r="F95" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="G95" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="H95" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="I95" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="J95" s="19"/>
+      <c r="L95" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="M95" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E95" s="22"/>
-      <c r="F95" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="G95" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="H95" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="I95" s="27" t="s">
+      <c r="N95" s="9" t="s">
         <v>46</v>
-      </c>
-      <c r="J95" s="21"/>
-      <c r="L95" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="M95" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="N95" s="9" t="s">
-        <v>47</v>
       </c>
       <c r="O95" s="9">
         <v>0</v>
@@ -4065,62 +4065,62 @@
       <c r="U95" s="10"/>
     </row>
     <row r="96" spans="2:22">
-      <c r="C96" s="21"/>
-      <c r="D96" s="19"/>
-      <c r="E96" s="22"/>
-      <c r="F96" s="20"/>
-      <c r="G96" s="21"/>
-      <c r="H96" s="21"/>
+      <c r="C96" s="19"/>
+      <c r="D96" s="20"/>
+      <c r="E96" s="25"/>
+      <c r="F96" s="24"/>
+      <c r="G96" s="19"/>
+      <c r="H96" s="19"/>
       <c r="I96" s="28"/>
-      <c r="J96" s="21"/>
+      <c r="J96" s="19"/>
       <c r="L96" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M96" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="N96" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="O96" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="P96" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="N96" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="O96" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="P96" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="11" t="s">
-        <v>38</v>
-      </c>
       <c r="R96" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S96" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T96" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U96" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="V96" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="97" spans="2:22">
-      <c r="C97" s="21"/>
-      <c r="D97" s="19"/>
-      <c r="E97" s="22"/>
-      <c r="F97" s="20"/>
-      <c r="G97" s="21"/>
-      <c r="H97" s="21"/>
+      <c r="C97" s="19"/>
+      <c r="D97" s="20"/>
+      <c r="E97" s="25"/>
+      <c r="F97" s="24"/>
+      <c r="G97" s="19"/>
+      <c r="H97" s="19"/>
       <c r="I97" s="28"/>
-      <c r="J97" s="21"/>
+      <c r="J97" s="19"/>
       <c r="L97" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M97" s="13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N97" s="10"/>
       <c r="O97" s="10"/>
@@ -4128,62 +4128,62 @@
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
       <c r="S97" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T97" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U97" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V97" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="98" spans="2:22">
-      <c r="C98" s="21"/>
-      <c r="D98" s="19"/>
-      <c r="E98" s="22"/>
-      <c r="F98" s="20"/>
-      <c r="G98" s="21"/>
-      <c r="H98" s="21"/>
+      <c r="C98" s="19"/>
+      <c r="D98" s="20"/>
+      <c r="E98" s="25"/>
+      <c r="F98" s="24"/>
+      <c r="G98" s="19"/>
+      <c r="H98" s="19"/>
       <c r="I98" s="28"/>
-      <c r="J98" s="21"/>
+      <c r="J98" s="19"/>
       <c r="L98" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M98" s="14"/>
       <c r="N98" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O98" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P98" s="14"/>
       <c r="Q98" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R98" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S98" s="10"/>
       <c r="T98" s="10"/>
       <c r="U98" s="10"/>
     </row>
     <row r="99" spans="2:22">
-      <c r="C99" s="21"/>
-      <c r="D99" s="19"/>
-      <c r="E99" s="22"/>
-      <c r="F99" s="20"/>
-      <c r="G99" s="21"/>
-      <c r="H99" s="21"/>
+      <c r="C99" s="19"/>
+      <c r="D99" s="20"/>
+      <c r="E99" s="25"/>
+      <c r="F99" s="24"/>
+      <c r="G99" s="19"/>
+      <c r="H99" s="19"/>
       <c r="I99" s="28"/>
-      <c r="J99" s="21"/>
+      <c r="J99" s="19"/>
       <c r="L99" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M99" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N99" s="10"/>
       <c r="O99" s="10"/>
@@ -4194,34 +4194,34 @@
       <c r="U99" s="10"/>
     </row>
     <row r="100" spans="2:22">
-      <c r="C100" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="D100" s="21"/>
-      <c r="E100" s="21"/>
-      <c r="F100" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="G100" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="H100" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="I100" s="19" t="s">
+      <c r="C100" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D100" s="19"/>
+      <c r="E100" s="19"/>
+      <c r="F100" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="G100" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="H100" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="I100" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="J100" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="L100" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="M100" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="J100" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="L100" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="M100" s="9" t="s">
-        <v>36</v>
-      </c>
       <c r="N100" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O100" s="9">
         <v>0</v>
@@ -4236,62 +4236,62 @@
       <c r="U100" s="10"/>
     </row>
     <row r="101" spans="2:22">
-      <c r="C101" s="21"/>
-      <c r="D101" s="21"/>
-      <c r="E101" s="21"/>
-      <c r="F101" s="21"/>
-      <c r="G101" s="21"/>
-      <c r="H101" s="21"/>
-      <c r="I101" s="19"/>
-      <c r="J101" s="20"/>
+      <c r="C101" s="19"/>
+      <c r="D101" s="19"/>
+      <c r="E101" s="19"/>
+      <c r="F101" s="19"/>
+      <c r="G101" s="19"/>
+      <c r="H101" s="19"/>
+      <c r="I101" s="20"/>
+      <c r="J101" s="24"/>
       <c r="L101" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M101" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N101" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O101" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P101" s="11">
         <v>0</v>
       </c>
       <c r="Q101" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="R101" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="R101" s="11" t="s">
-        <v>77</v>
-      </c>
       <c r="S101" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T101" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U101" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="V101" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="102" spans="2:22">
-      <c r="C102" s="21"/>
-      <c r="D102" s="21"/>
-      <c r="E102" s="21"/>
-      <c r="F102" s="21"/>
-      <c r="G102" s="21"/>
-      <c r="H102" s="21"/>
-      <c r="I102" s="19"/>
-      <c r="J102" s="20"/>
+      <c r="C102" s="19"/>
+      <c r="D102" s="19"/>
+      <c r="E102" s="19"/>
+      <c r="F102" s="19"/>
+      <c r="G102" s="19"/>
+      <c r="H102" s="19"/>
+      <c r="I102" s="20"/>
+      <c r="J102" s="24"/>
       <c r="L102" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M102" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N102" s="10"/>
       <c r="O102" s="10"/>
@@ -4299,62 +4299,62 @@
       <c r="Q102" s="10"/>
       <c r="R102" s="10"/>
       <c r="S102" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T102" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U102" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V102" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="103" spans="2:22">
-      <c r="C103" s="21"/>
-      <c r="D103" s="21"/>
-      <c r="E103" s="21"/>
-      <c r="F103" s="21"/>
-      <c r="G103" s="21"/>
-      <c r="H103" s="21"/>
-      <c r="I103" s="19"/>
-      <c r="J103" s="20"/>
+      <c r="C103" s="19"/>
+      <c r="D103" s="19"/>
+      <c r="E103" s="19"/>
+      <c r="F103" s="19"/>
+      <c r="G103" s="19"/>
+      <c r="H103" s="19"/>
+      <c r="I103" s="20"/>
+      <c r="J103" s="24"/>
       <c r="L103" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M103" s="14"/>
       <c r="N103" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O103" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P103" s="14"/>
       <c r="Q103" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R103" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S103" s="10"/>
       <c r="T103" s="10"/>
       <c r="U103" s="10"/>
     </row>
     <row r="104" spans="2:22">
-      <c r="C104" s="21"/>
-      <c r="D104" s="21"/>
-      <c r="E104" s="21"/>
-      <c r="F104" s="21"/>
-      <c r="G104" s="21"/>
-      <c r="H104" s="21"/>
-      <c r="I104" s="19"/>
-      <c r="J104" s="20"/>
+      <c r="C104" s="19"/>
+      <c r="D104" s="19"/>
+      <c r="E104" s="19"/>
+      <c r="F104" s="19"/>
+      <c r="G104" s="19"/>
+      <c r="H104" s="19"/>
+      <c r="I104" s="20"/>
+      <c r="J104" s="24"/>
       <c r="L104" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M104" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N104" s="10"/>
       <c r="O104" s="10"/>
@@ -4367,38 +4367,38 @@
     </row>
     <row r="105" spans="2:22">
       <c r="B105" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C105" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D105" s="21"/>
-      <c r="E105" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="F105" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C105" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="D105" s="19"/>
+      <c r="E105" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="F105" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G105" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H105" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I105" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="J105" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="L105" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="M105" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="G105" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="H105" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="I105" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="J105" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="L105" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="M105" s="9" t="s">
-        <v>36</v>
-      </c>
       <c r="N105" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O105" s="9">
         <v>0</v>
@@ -4416,65 +4416,65 @@
       <c r="B106">
         <v>7</v>
       </c>
-      <c r="C106" s="21"/>
-      <c r="D106" s="21"/>
-      <c r="E106" s="22"/>
-      <c r="F106" s="19"/>
-      <c r="G106" s="19"/>
-      <c r="H106" s="19"/>
-      <c r="I106" s="20"/>
-      <c r="J106" s="26"/>
+      <c r="C106" s="19"/>
+      <c r="D106" s="19"/>
+      <c r="E106" s="25"/>
+      <c r="F106" s="20"/>
+      <c r="G106" s="20"/>
+      <c r="H106" s="20"/>
+      <c r="I106" s="24"/>
+      <c r="J106" s="29"/>
       <c r="L106" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M106" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N106" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O106" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P106" s="11">
         <v>1</v>
       </c>
       <c r="Q106" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="R106" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="S106" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T106" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U106" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V106" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="107" spans="2:22">
       <c r="B107" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C107" s="21"/>
-      <c r="D107" s="21"/>
-      <c r="E107" s="22"/>
-      <c r="F107" s="19"/>
-      <c r="G107" s="19"/>
-      <c r="H107" s="19"/>
-      <c r="I107" s="20"/>
-      <c r="J107" s="26"/>
+        <v>51</v>
+      </c>
+      <c r="C107" s="19"/>
+      <c r="D107" s="19"/>
+      <c r="E107" s="25"/>
+      <c r="F107" s="20"/>
+      <c r="G107" s="20"/>
+      <c r="H107" s="20"/>
+      <c r="I107" s="24"/>
+      <c r="J107" s="29"/>
       <c r="L107" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M107" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N107" s="10"/>
       <c r="O107" s="10"/>
@@ -4482,30 +4482,30 @@
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
       <c r="S107" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T107" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U107" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="V107" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="108" spans="2:22">
       <c r="B108">
         <v>4</v>
       </c>
-      <c r="C108" s="21"/>
-      <c r="D108" s="21"/>
-      <c r="E108" s="22"/>
-      <c r="F108" s="19"/>
-      <c r="G108" s="19"/>
-      <c r="H108" s="19"/>
-      <c r="I108" s="20"/>
-      <c r="J108" s="26"/>
+      <c r="C108" s="19"/>
+      <c r="D108" s="19"/>
+      <c r="E108" s="25"/>
+      <c r="F108" s="20"/>
+      <c r="G108" s="20"/>
+      <c r="H108" s="20"/>
+      <c r="I108" s="24"/>
+      <c r="J108" s="29"/>
       <c r="L108" s="14" t="s">
         <v>17</v>
       </c>
@@ -4515,7 +4515,7 @@
         <v>768</v>
       </c>
       <c r="O108" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P108" s="14"/>
       <c r="Q108" s="5">
@@ -4523,34 +4523,34 @@
         <v>1344</v>
       </c>
       <c r="R108" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S108" s="10"/>
       <c r="T108" s="10"/>
       <c r="U108" s="10"/>
     </row>
     <row r="109" spans="2:22">
-      <c r="C109" s="21"/>
-      <c r="D109" s="21"/>
-      <c r="E109" s="22"/>
-      <c r="F109" s="19"/>
-      <c r="G109" s="19"/>
-      <c r="H109" s="19"/>
-      <c r="I109" s="20"/>
-      <c r="J109" s="26"/>
+      <c r="C109" s="19"/>
+      <c r="D109" s="19"/>
+      <c r="E109" s="25"/>
+      <c r="F109" s="20"/>
+      <c r="G109" s="20"/>
+      <c r="H109" s="20"/>
+      <c r="I109" s="24"/>
+      <c r="J109" s="29"/>
       <c r="L109" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M109" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O109" s="10"/>
       <c r="P109" s="10"/>
       <c r="Q109" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="R109" s="10"/>
       <c r="S109" s="10"/>
@@ -4561,34 +4561,34 @@
       <c r="P110" s="10"/>
     </row>
     <row r="111" spans="2:22">
-      <c r="C111" s="21" t="s">
+      <c r="C111" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="D111" s="20"/>
+      <c r="E111" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="D111" s="19"/>
-      <c r="E111" s="19" t="s">
+      <c r="F111" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="G111" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="H111" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="I111" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="J111" s="19"/>
+      <c r="L111" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="M111" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F111" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="G111" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="H111" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="I111" s="27" t="s">
+      <c r="N111" s="9" t="s">
         <v>46</v>
-      </c>
-      <c r="J111" s="21"/>
-      <c r="L111" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="M111" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="N111" s="9" t="s">
-        <v>47</v>
       </c>
       <c r="O111" s="9">
         <v>0</v>
@@ -4603,62 +4603,62 @@
       <c r="U111" s="10"/>
     </row>
     <row r="112" spans="2:22">
-      <c r="C112" s="21"/>
-      <c r="D112" s="19"/>
-      <c r="E112" s="19"/>
-      <c r="F112" s="21"/>
-      <c r="G112" s="20"/>
-      <c r="H112" s="21"/>
+      <c r="C112" s="19"/>
+      <c r="D112" s="20"/>
+      <c r="E112" s="20"/>
+      <c r="F112" s="19"/>
+      <c r="G112" s="24"/>
+      <c r="H112" s="19"/>
       <c r="I112" s="28"/>
-      <c r="J112" s="21"/>
+      <c r="J112" s="19"/>
       <c r="L112" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M112" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="N112" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="O112" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="P112" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q112" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="N112" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="O112" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="P112" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q112" s="11" t="s">
-        <v>38</v>
-      </c>
       <c r="R112" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S112" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T112" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U112" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="V112" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="113" spans="2:22">
-      <c r="C113" s="21"/>
-      <c r="D113" s="19"/>
-      <c r="E113" s="19"/>
-      <c r="F113" s="21"/>
-      <c r="G113" s="20"/>
-      <c r="H113" s="21"/>
+      <c r="C113" s="19"/>
+      <c r="D113" s="20"/>
+      <c r="E113" s="20"/>
+      <c r="F113" s="19"/>
+      <c r="G113" s="24"/>
+      <c r="H113" s="19"/>
       <c r="I113" s="28"/>
-      <c r="J113" s="21"/>
+      <c r="J113" s="19"/>
       <c r="L113" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M113" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N113" s="10"/>
       <c r="O113" s="10"/>
@@ -4666,62 +4666,62 @@
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
       <c r="S113" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T113" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U113" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V113" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="114" spans="2:22">
-      <c r="C114" s="21"/>
-      <c r="D114" s="19"/>
-      <c r="E114" s="19"/>
-      <c r="F114" s="21"/>
-      <c r="G114" s="20"/>
-      <c r="H114" s="21"/>
+      <c r="C114" s="19"/>
+      <c r="D114" s="20"/>
+      <c r="E114" s="20"/>
+      <c r="F114" s="19"/>
+      <c r="G114" s="24"/>
+      <c r="H114" s="19"/>
       <c r="I114" s="28"/>
-      <c r="J114" s="21"/>
+      <c r="J114" s="19"/>
       <c r="L114" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M114" s="14"/>
       <c r="N114" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O114" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P114" s="14"/>
       <c r="Q114" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R114" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S114" s="10"/>
       <c r="T114" s="10"/>
       <c r="U114" s="10"/>
     </row>
     <row r="115" spans="2:22">
-      <c r="C115" s="21"/>
-      <c r="D115" s="19"/>
-      <c r="E115" s="19"/>
-      <c r="F115" s="21"/>
-      <c r="G115" s="20"/>
-      <c r="H115" s="21"/>
+      <c r="C115" s="19"/>
+      <c r="D115" s="20"/>
+      <c r="E115" s="20"/>
+      <c r="F115" s="19"/>
+      <c r="G115" s="24"/>
+      <c r="H115" s="19"/>
       <c r="I115" s="28"/>
-      <c r="J115" s="21"/>
+      <c r="J115" s="19"/>
       <c r="L115" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M115" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N115" s="10"/>
       <c r="O115" s="10"/>
@@ -4732,34 +4732,34 @@
       <c r="U115" s="10"/>
     </row>
     <row r="116" spans="2:22">
-      <c r="C116" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="D116" s="21"/>
-      <c r="E116" s="21"/>
-      <c r="F116" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="G116" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="H116" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="I116" s="19" t="s">
+      <c r="C116" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D116" s="19"/>
+      <c r="E116" s="19"/>
+      <c r="F116" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="G116" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="H116" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="I116" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="J116" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="L116" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="M116" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="J116" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="L116" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="M116" s="9" t="s">
-        <v>36</v>
-      </c>
       <c r="N116" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O116" s="9">
         <v>0</v>
@@ -4774,62 +4774,62 @@
       <c r="U116" s="10"/>
     </row>
     <row r="117" spans="2:22">
-      <c r="C117" s="21"/>
-      <c r="D117" s="21"/>
-      <c r="E117" s="21"/>
-      <c r="F117" s="21"/>
-      <c r="G117" s="21"/>
-      <c r="H117" s="21"/>
-      <c r="I117" s="19"/>
-      <c r="J117" s="20"/>
+      <c r="C117" s="19"/>
+      <c r="D117" s="19"/>
+      <c r="E117" s="19"/>
+      <c r="F117" s="19"/>
+      <c r="G117" s="19"/>
+      <c r="H117" s="19"/>
+      <c r="I117" s="20"/>
+      <c r="J117" s="24"/>
       <c r="L117" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M117" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N117" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O117" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P117" s="11">
         <v>0</v>
       </c>
       <c r="Q117" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="R117" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="R117" s="11" t="s">
-        <v>77</v>
-      </c>
       <c r="S117" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T117" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U117" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="V117" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="118" spans="2:22">
-      <c r="C118" s="21"/>
-      <c r="D118" s="21"/>
-      <c r="E118" s="21"/>
-      <c r="F118" s="21"/>
-      <c r="G118" s="21"/>
-      <c r="H118" s="21"/>
-      <c r="I118" s="19"/>
-      <c r="J118" s="20"/>
+      <c r="C118" s="19"/>
+      <c r="D118" s="19"/>
+      <c r="E118" s="19"/>
+      <c r="F118" s="19"/>
+      <c r="G118" s="19"/>
+      <c r="H118" s="19"/>
+      <c r="I118" s="20"/>
+      <c r="J118" s="24"/>
       <c r="L118" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M118" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N118" s="10"/>
       <c r="O118" s="10"/>
@@ -4837,62 +4837,62 @@
       <c r="Q118" s="10"/>
       <c r="R118" s="10"/>
       <c r="S118" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T118" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U118" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V118" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="119" spans="2:22">
-      <c r="C119" s="21"/>
-      <c r="D119" s="21"/>
-      <c r="E119" s="21"/>
-      <c r="F119" s="21"/>
-      <c r="G119" s="21"/>
-      <c r="H119" s="21"/>
-      <c r="I119" s="19"/>
-      <c r="J119" s="20"/>
+      <c r="C119" s="19"/>
+      <c r="D119" s="19"/>
+      <c r="E119" s="19"/>
+      <c r="F119" s="19"/>
+      <c r="G119" s="19"/>
+      <c r="H119" s="19"/>
+      <c r="I119" s="20"/>
+      <c r="J119" s="24"/>
       <c r="L119" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M119" s="14"/>
       <c r="N119" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O119" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P119" s="14"/>
       <c r="Q119" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R119" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S119" s="10"/>
       <c r="T119" s="10"/>
       <c r="U119" s="10"/>
     </row>
     <row r="120" spans="2:22">
-      <c r="C120" s="21"/>
-      <c r="D120" s="21"/>
-      <c r="E120" s="21"/>
-      <c r="F120" s="21"/>
-      <c r="G120" s="21"/>
-      <c r="H120" s="21"/>
-      <c r="I120" s="19"/>
-      <c r="J120" s="20"/>
+      <c r="C120" s="19"/>
+      <c r="D120" s="19"/>
+      <c r="E120" s="19"/>
+      <c r="F120" s="19"/>
+      <c r="G120" s="19"/>
+      <c r="H120" s="19"/>
+      <c r="I120" s="20"/>
+      <c r="J120" s="24"/>
       <c r="L120" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M120" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N120" s="10"/>
       <c r="O120" s="10"/>
@@ -4904,34 +4904,34 @@
       <c r="U120" s="10"/>
     </row>
     <row r="121" spans="2:22">
-      <c r="C121" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D121" s="21"/>
-      <c r="E121" s="22"/>
-      <c r="F121" s="19" t="s">
+      <c r="C121" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="D121" s="19"/>
+      <c r="E121" s="25"/>
+      <c r="F121" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G121" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H121" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I121" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="J121" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="L121" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="M121" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="G121" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="H121" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="I121" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="J121" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="L121" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="M121" s="9" t="s">
-        <v>36</v>
-      </c>
       <c r="N121" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O121" s="9">
         <v>0</v>
@@ -4946,65 +4946,65 @@
       <c r="U121" s="10"/>
     </row>
     <row r="122" spans="2:22">
-      <c r="C122" s="21"/>
-      <c r="D122" s="21"/>
-      <c r="E122" s="22"/>
-      <c r="F122" s="19"/>
-      <c r="G122" s="19"/>
-      <c r="H122" s="19"/>
-      <c r="I122" s="20"/>
-      <c r="J122" s="26"/>
+      <c r="C122" s="19"/>
+      <c r="D122" s="19"/>
+      <c r="E122" s="25"/>
+      <c r="F122" s="20"/>
+      <c r="G122" s="20"/>
+      <c r="H122" s="20"/>
+      <c r="I122" s="24"/>
+      <c r="J122" s="29"/>
       <c r="L122" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M122" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N122" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O122" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P122" s="11">
         <v>1</v>
       </c>
       <c r="Q122" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="R122" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="S122" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T122" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U122" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V122" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="123" spans="2:22">
       <c r="B123" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C123" s="21"/>
-      <c r="D123" s="21"/>
-      <c r="E123" s="22"/>
-      <c r="F123" s="19"/>
-      <c r="G123" s="19"/>
-      <c r="H123" s="19"/>
-      <c r="I123" s="20"/>
-      <c r="J123" s="26"/>
+        <v>51</v>
+      </c>
+      <c r="C123" s="19"/>
+      <c r="D123" s="19"/>
+      <c r="E123" s="25"/>
+      <c r="F123" s="20"/>
+      <c r="G123" s="20"/>
+      <c r="H123" s="20"/>
+      <c r="I123" s="24"/>
+      <c r="J123" s="29"/>
       <c r="L123" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M123" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N123" s="10"/>
       <c r="O123" s="10"/>
@@ -5012,30 +5012,30 @@
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
       <c r="S123" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T123" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U123" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="V123" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="124" spans="2:22">
       <c r="B124">
         <v>5</v>
       </c>
-      <c r="C124" s="21"/>
-      <c r="D124" s="21"/>
-      <c r="E124" s="22"/>
-      <c r="F124" s="19"/>
-      <c r="G124" s="19"/>
-      <c r="H124" s="19"/>
-      <c r="I124" s="20"/>
-      <c r="J124" s="26"/>
+      <c r="C124" s="19"/>
+      <c r="D124" s="19"/>
+      <c r="E124" s="25"/>
+      <c r="F124" s="20"/>
+      <c r="G124" s="20"/>
+      <c r="H124" s="20"/>
+      <c r="I124" s="24"/>
+      <c r="J124" s="29"/>
       <c r="L124" s="14" t="s">
         <v>17</v>
       </c>
@@ -5045,36 +5045,36 @@
         <v>960</v>
       </c>
       <c r="O124" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P124" s="14"/>
       <c r="Q124" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R124" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S124" s="10"/>
       <c r="T124" s="10"/>
       <c r="U124" s="10"/>
     </row>
     <row r="125" spans="2:22">
-      <c r="C125" s="21"/>
-      <c r="D125" s="21"/>
-      <c r="E125" s="22"/>
-      <c r="F125" s="19"/>
-      <c r="G125" s="19"/>
-      <c r="H125" s="19"/>
-      <c r="I125" s="20"/>
-      <c r="J125" s="26"/>
+      <c r="C125" s="19"/>
+      <c r="D125" s="19"/>
+      <c r="E125" s="25"/>
+      <c r="F125" s="20"/>
+      <c r="G125" s="20"/>
+      <c r="H125" s="20"/>
+      <c r="I125" s="24"/>
+      <c r="J125" s="29"/>
       <c r="L125" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M125" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O125" s="10"/>
       <c r="P125" s="10"/>
@@ -5088,30 +5088,30 @@
       <c r="P126" s="10"/>
     </row>
     <row r="127" spans="2:22">
-      <c r="C127" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="D127" s="19"/>
-      <c r="E127" s="22"/>
-      <c r="F127" s="21" t="s">
+      <c r="C127" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="D127" s="20"/>
+      <c r="E127" s="25"/>
+      <c r="F127" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="G127" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="H127" s="19"/>
+      <c r="I127" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="J127" s="19"/>
+      <c r="L127" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="M127" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="G127" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="H127" s="21"/>
-      <c r="I127" s="27" t="s">
+      <c r="N127" s="9" t="s">
         <v>46</v>
-      </c>
-      <c r="J127" s="21"/>
-      <c r="L127" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="M127" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="N127" s="9" t="s">
-        <v>47</v>
       </c>
       <c r="O127" s="9">
         <v>0</v>
@@ -5126,62 +5126,62 @@
       <c r="U127" s="10"/>
     </row>
     <row r="128" spans="2:22">
-      <c r="C128" s="21"/>
-      <c r="D128" s="19"/>
-      <c r="E128" s="22"/>
-      <c r="F128" s="21"/>
-      <c r="G128" s="21"/>
-      <c r="H128" s="21"/>
+      <c r="C128" s="19"/>
+      <c r="D128" s="20"/>
+      <c r="E128" s="25"/>
+      <c r="F128" s="19"/>
+      <c r="G128" s="19"/>
+      <c r="H128" s="19"/>
       <c r="I128" s="28"/>
-      <c r="J128" s="21"/>
+      <c r="J128" s="19"/>
       <c r="L128" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M128" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N128" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O128" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P128" s="11">
         <v>0</v>
       </c>
       <c r="Q128" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R128" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S128" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="T128" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="U128" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="V128" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="129" spans="2:22">
-      <c r="C129" s="21"/>
-      <c r="D129" s="19"/>
-      <c r="E129" s="22"/>
-      <c r="F129" s="21"/>
-      <c r="G129" s="21"/>
-      <c r="H129" s="21"/>
+      <c r="C129" s="19"/>
+      <c r="D129" s="20"/>
+      <c r="E129" s="25"/>
+      <c r="F129" s="19"/>
+      <c r="G129" s="19"/>
+      <c r="H129" s="19"/>
       <c r="I129" s="28"/>
-      <c r="J129" s="21"/>
+      <c r="J129" s="19"/>
       <c r="L129" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M129" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N129" s="10"/>
       <c r="O129" s="10"/>
@@ -5194,49 +5194,49 @@
       <c r="V129" s="10"/>
     </row>
     <row r="130" spans="2:22">
-      <c r="C130" s="21"/>
-      <c r="D130" s="19"/>
-      <c r="E130" s="22"/>
-      <c r="F130" s="21"/>
-      <c r="G130" s="21"/>
-      <c r="H130" s="21"/>
+      <c r="C130" s="19"/>
+      <c r="D130" s="20"/>
+      <c r="E130" s="25"/>
+      <c r="F130" s="19"/>
+      <c r="G130" s="19"/>
+      <c r="H130" s="19"/>
       <c r="I130" s="28"/>
-      <c r="J130" s="21"/>
+      <c r="J130" s="19"/>
       <c r="L130" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M130" s="14"/>
       <c r="N130" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O130" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P130" s="14"/>
       <c r="Q130" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R130" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S130" s="10"/>
       <c r="T130" s="10"/>
       <c r="U130" s="10"/>
     </row>
     <row r="131" spans="2:22">
-      <c r="C131" s="21"/>
-      <c r="D131" s="19"/>
-      <c r="E131" s="22"/>
-      <c r="F131" s="21"/>
-      <c r="G131" s="21"/>
-      <c r="H131" s="21"/>
+      <c r="C131" s="19"/>
+      <c r="D131" s="20"/>
+      <c r="E131" s="25"/>
+      <c r="F131" s="19"/>
+      <c r="G131" s="19"/>
+      <c r="H131" s="19"/>
       <c r="I131" s="28"/>
-      <c r="J131" s="21"/>
+      <c r="J131" s="19"/>
       <c r="L131" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M131" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N131" s="10"/>
       <c r="O131" s="10"/>
@@ -5248,32 +5248,32 @@
       <c r="U131" s="10"/>
     </row>
     <row r="132" spans="2:22">
-      <c r="C132" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="D132" s="21"/>
-      <c r="E132" s="21"/>
-      <c r="F132" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="G132" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="H132" s="21"/>
-      <c r="I132" s="19" t="s">
+      <c r="C132" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D132" s="19"/>
+      <c r="E132" s="19"/>
+      <c r="F132" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="G132" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="H132" s="19"/>
+      <c r="I132" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="J132" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="L132" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="M132" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="J132" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="L132" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="M132" s="9" t="s">
-        <v>36</v>
-      </c>
       <c r="N132" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O132" s="9">
         <v>0</v>
@@ -5288,62 +5288,62 @@
       <c r="U132" s="10"/>
     </row>
     <row r="133" spans="2:22">
-      <c r="C133" s="21"/>
-      <c r="D133" s="21"/>
-      <c r="E133" s="21"/>
-      <c r="F133" s="21"/>
-      <c r="G133" s="21"/>
-      <c r="H133" s="21"/>
-      <c r="I133" s="19"/>
-      <c r="J133" s="20"/>
+      <c r="C133" s="19"/>
+      <c r="D133" s="19"/>
+      <c r="E133" s="19"/>
+      <c r="F133" s="19"/>
+      <c r="G133" s="19"/>
+      <c r="H133" s="19"/>
+      <c r="I133" s="20"/>
+      <c r="J133" s="24"/>
       <c r="L133" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M133" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N133" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O133" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P133" s="11">
         <v>0</v>
       </c>
       <c r="Q133" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="R133" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="R133" s="11" t="s">
-        <v>77</v>
-      </c>
       <c r="S133" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T133" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U133" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="V133" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="134" spans="2:22">
-      <c r="C134" s="21"/>
-      <c r="D134" s="21"/>
-      <c r="E134" s="21"/>
-      <c r="F134" s="21"/>
-      <c r="G134" s="21"/>
-      <c r="H134" s="21"/>
-      <c r="I134" s="19"/>
-      <c r="J134" s="20"/>
+      <c r="C134" s="19"/>
+      <c r="D134" s="19"/>
+      <c r="E134" s="19"/>
+      <c r="F134" s="19"/>
+      <c r="G134" s="19"/>
+      <c r="H134" s="19"/>
+      <c r="I134" s="20"/>
+      <c r="J134" s="24"/>
       <c r="L134" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M134" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N134" s="10"/>
       <c r="O134" s="10"/>
@@ -5351,62 +5351,62 @@
       <c r="Q134" s="10"/>
       <c r="R134" s="10"/>
       <c r="S134" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T134" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U134" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V134" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="135" spans="2:22">
-      <c r="C135" s="21"/>
-      <c r="D135" s="21"/>
-      <c r="E135" s="21"/>
-      <c r="F135" s="21"/>
-      <c r="G135" s="21"/>
-      <c r="H135" s="21"/>
-      <c r="I135" s="19"/>
-      <c r="J135" s="20"/>
+      <c r="C135" s="19"/>
+      <c r="D135" s="19"/>
+      <c r="E135" s="19"/>
+      <c r="F135" s="19"/>
+      <c r="G135" s="19"/>
+      <c r="H135" s="19"/>
+      <c r="I135" s="20"/>
+      <c r="J135" s="24"/>
       <c r="L135" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M135" s="14"/>
       <c r="N135" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O135" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P135" s="14"/>
       <c r="Q135" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R135" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S135" s="10"/>
       <c r="T135" s="10"/>
       <c r="U135" s="10"/>
     </row>
     <row r="136" spans="2:22">
-      <c r="C136" s="21"/>
-      <c r="D136" s="21"/>
-      <c r="E136" s="21"/>
-      <c r="F136" s="21"/>
-      <c r="G136" s="21"/>
-      <c r="H136" s="21"/>
-      <c r="I136" s="19"/>
-      <c r="J136" s="20"/>
+      <c r="C136" s="19"/>
+      <c r="D136" s="19"/>
+      <c r="E136" s="19"/>
+      <c r="F136" s="19"/>
+      <c r="G136" s="19"/>
+      <c r="H136" s="19"/>
+      <c r="I136" s="20"/>
+      <c r="J136" s="24"/>
       <c r="L136" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M136" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N136" s="10"/>
       <c r="O136" s="10"/>
@@ -5418,32 +5418,32 @@
       <c r="U136" s="10"/>
     </row>
     <row r="137" spans="2:22">
-      <c r="C137" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D137" s="21"/>
-      <c r="E137" s="22"/>
-      <c r="F137" s="19" t="s">
+      <c r="C137" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="D137" s="19"/>
+      <c r="E137" s="25"/>
+      <c r="F137" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G137" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H137" s="20"/>
+      <c r="I137" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="J137" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="L137" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="M137" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="G137" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="H137" s="19"/>
-      <c r="I137" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="J137" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="L137" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="M137" s="9" t="s">
-        <v>36</v>
-      </c>
       <c r="N137" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O137" s="9">
         <v>0</v>
@@ -5458,65 +5458,65 @@
       <c r="U137" s="10"/>
     </row>
     <row r="138" spans="2:22">
-      <c r="C138" s="21"/>
-      <c r="D138" s="21"/>
-      <c r="E138" s="22"/>
-      <c r="F138" s="19"/>
-      <c r="G138" s="19"/>
-      <c r="H138" s="19"/>
-      <c r="I138" s="20"/>
-      <c r="J138" s="26"/>
+      <c r="C138" s="19"/>
+      <c r="D138" s="19"/>
+      <c r="E138" s="25"/>
+      <c r="F138" s="20"/>
+      <c r="G138" s="20"/>
+      <c r="H138" s="20"/>
+      <c r="I138" s="24"/>
+      <c r="J138" s="29"/>
       <c r="L138" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M138" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N138" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O138" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P138" s="11">
         <v>1</v>
       </c>
       <c r="Q138" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="R138" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="S138" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T138" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U138" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V138" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="139" spans="2:22">
       <c r="B139" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C139" s="21"/>
-      <c r="D139" s="21"/>
-      <c r="E139" s="22"/>
-      <c r="F139" s="19"/>
-      <c r="G139" s="19"/>
-      <c r="H139" s="19"/>
-      <c r="I139" s="20"/>
-      <c r="J139" s="26"/>
+        <v>51</v>
+      </c>
+      <c r="C139" s="19"/>
+      <c r="D139" s="19"/>
+      <c r="E139" s="25"/>
+      <c r="F139" s="20"/>
+      <c r="G139" s="20"/>
+      <c r="H139" s="20"/>
+      <c r="I139" s="24"/>
+      <c r="J139" s="29"/>
       <c r="L139" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M139" s="13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="N139" s="10"/>
       <c r="O139" s="10"/>
@@ -5524,30 +5524,30 @@
       <c r="Q139" s="10"/>
       <c r="R139" s="10"/>
       <c r="S139" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T139" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U139" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="V139" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="140" spans="2:22">
       <c r="B140">
         <v>6</v>
       </c>
-      <c r="C140" s="21"/>
-      <c r="D140" s="21"/>
-      <c r="E140" s="22"/>
-      <c r="F140" s="19"/>
-      <c r="G140" s="19"/>
-      <c r="H140" s="19"/>
-      <c r="I140" s="20"/>
-      <c r="J140" s="26"/>
+      <c r="C140" s="19"/>
+      <c r="D140" s="19"/>
+      <c r="E140" s="25"/>
+      <c r="F140" s="20"/>
+      <c r="G140" s="20"/>
+      <c r="H140" s="20"/>
+      <c r="I140" s="24"/>
+      <c r="J140" s="29"/>
       <c r="L140" s="14" t="s">
         <v>17</v>
       </c>
@@ -5557,36 +5557,36 @@
         <v>1152</v>
       </c>
       <c r="O140" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P140" s="14"/>
       <c r="Q140" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R140" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S140" s="10"/>
       <c r="T140" s="10"/>
       <c r="U140" s="10"/>
     </row>
     <row r="141" spans="2:22">
-      <c r="C141" s="21"/>
-      <c r="D141" s="21"/>
-      <c r="E141" s="22"/>
-      <c r="F141" s="19"/>
-      <c r="G141" s="19"/>
-      <c r="H141" s="19"/>
-      <c r="I141" s="20"/>
-      <c r="J141" s="26"/>
+      <c r="C141" s="19"/>
+      <c r="D141" s="19"/>
+      <c r="E141" s="25"/>
+      <c r="F141" s="20"/>
+      <c r="G141" s="20"/>
+      <c r="H141" s="20"/>
+      <c r="I141" s="24"/>
+      <c r="J141" s="29"/>
       <c r="L141" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M141" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N141" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="O141" s="10"/>
       <c r="P141" s="10"/>
@@ -5600,26 +5600,26 @@
       <c r="P142" s="10"/>
     </row>
     <row r="143" spans="2:22">
-      <c r="C143" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="D143" s="21"/>
-      <c r="E143" s="22"/>
-      <c r="F143" s="22"/>
-      <c r="G143" s="21"/>
-      <c r="H143" s="21"/>
+      <c r="C143" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="D143" s="19"/>
+      <c r="E143" s="25"/>
+      <c r="F143" s="25"/>
+      <c r="G143" s="19"/>
+      <c r="H143" s="19"/>
       <c r="I143" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="J143" s="19"/>
+      <c r="L143" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="M143" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="N143" s="9" t="s">
         <v>46</v>
-      </c>
-      <c r="J143" s="21"/>
-      <c r="L143" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="M143" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="N143" s="9" t="s">
-        <v>47</v>
       </c>
       <c r="O143" s="9">
         <v>0</v>
@@ -5634,62 +5634,62 @@
       <c r="U143" s="10"/>
     </row>
     <row r="144" spans="2:22">
-      <c r="C144" s="21"/>
-      <c r="D144" s="21"/>
-      <c r="E144" s="22"/>
-      <c r="F144" s="22"/>
-      <c r="G144" s="21"/>
-      <c r="H144" s="21"/>
+      <c r="C144" s="19"/>
+      <c r="D144" s="19"/>
+      <c r="E144" s="25"/>
+      <c r="F144" s="25"/>
+      <c r="G144" s="19"/>
+      <c r="H144" s="19"/>
       <c r="I144" s="28"/>
-      <c r="J144" s="21"/>
+      <c r="J144" s="19"/>
       <c r="L144" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M144" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N144" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O144" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P144" s="11">
         <v>0</v>
       </c>
       <c r="Q144" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R144" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S144" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="T144" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="U144" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="V144" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="145" spans="2:22">
-      <c r="C145" s="21"/>
-      <c r="D145" s="21"/>
-      <c r="E145" s="22"/>
-      <c r="F145" s="22"/>
-      <c r="G145" s="21"/>
-      <c r="H145" s="21"/>
+      <c r="C145" s="19"/>
+      <c r="D145" s="19"/>
+      <c r="E145" s="25"/>
+      <c r="F145" s="25"/>
+      <c r="G145" s="19"/>
+      <c r="H145" s="19"/>
       <c r="I145" s="28"/>
-      <c r="J145" s="21"/>
+      <c r="J145" s="19"/>
       <c r="L145" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M145" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N145" s="10"/>
       <c r="O145" s="10"/>
@@ -5702,49 +5702,49 @@
       <c r="V145" s="10"/>
     </row>
     <row r="146" spans="2:22">
-      <c r="C146" s="21"/>
-      <c r="D146" s="21"/>
-      <c r="E146" s="22"/>
-      <c r="F146" s="22"/>
-      <c r="G146" s="21"/>
-      <c r="H146" s="21"/>
+      <c r="C146" s="19"/>
+      <c r="D146" s="19"/>
+      <c r="E146" s="25"/>
+      <c r="F146" s="25"/>
+      <c r="G146" s="19"/>
+      <c r="H146" s="19"/>
       <c r="I146" s="28"/>
-      <c r="J146" s="21"/>
+      <c r="J146" s="19"/>
       <c r="L146" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M146" s="14"/>
       <c r="N146" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O146" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P146" s="14"/>
       <c r="Q146" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R146" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S146" s="10"/>
       <c r="T146" s="10"/>
       <c r="U146" s="10"/>
     </row>
     <row r="147" spans="2:22">
-      <c r="C147" s="21"/>
-      <c r="D147" s="21"/>
-      <c r="E147" s="22"/>
-      <c r="F147" s="22"/>
-      <c r="G147" s="21"/>
-      <c r="H147" s="21"/>
+      <c r="C147" s="19"/>
+      <c r="D147" s="19"/>
+      <c r="E147" s="25"/>
+      <c r="F147" s="25"/>
+      <c r="G147" s="19"/>
+      <c r="H147" s="19"/>
       <c r="I147" s="28"/>
-      <c r="J147" s="21"/>
+      <c r="J147" s="19"/>
       <c r="L147" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M147" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N147" s="10"/>
       <c r="O147" s="10"/>
@@ -5756,28 +5756,28 @@
       <c r="U147" s="10"/>
     </row>
     <row r="148" spans="2:22">
-      <c r="C148" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="D148" s="21"/>
-      <c r="E148" s="22"/>
-      <c r="F148" s="22"/>
-      <c r="G148" s="21"/>
-      <c r="H148" s="21"/>
-      <c r="I148" s="19" t="s">
+      <c r="C148" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D148" s="19"/>
+      <c r="E148" s="25"/>
+      <c r="F148" s="25"/>
+      <c r="G148" s="19"/>
+      <c r="H148" s="19"/>
+      <c r="I148" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="J148" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="L148" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="M148" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="J148" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="L148" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="M148" s="9" t="s">
-        <v>36</v>
-      </c>
       <c r="N148" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O148" s="9">
         <v>0</v>
@@ -5792,62 +5792,62 @@
       <c r="U148" s="10"/>
     </row>
     <row r="149" spans="2:22">
-      <c r="C149" s="21"/>
-      <c r="D149" s="21"/>
-      <c r="E149" s="22"/>
-      <c r="F149" s="22"/>
-      <c r="G149" s="21"/>
-      <c r="H149" s="21"/>
-      <c r="I149" s="19"/>
-      <c r="J149" s="20"/>
+      <c r="C149" s="19"/>
+      <c r="D149" s="19"/>
+      <c r="E149" s="25"/>
+      <c r="F149" s="25"/>
+      <c r="G149" s="19"/>
+      <c r="H149" s="19"/>
+      <c r="I149" s="20"/>
+      <c r="J149" s="24"/>
       <c r="L149" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M149" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N149" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O149" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P149" s="11">
         <v>0</v>
       </c>
       <c r="Q149" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="R149" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="R149" s="11" t="s">
-        <v>77</v>
-      </c>
       <c r="S149" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T149" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U149" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="V149" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="150" spans="2:22">
-      <c r="C150" s="21"/>
-      <c r="D150" s="21"/>
-      <c r="E150" s="22"/>
-      <c r="F150" s="22"/>
-      <c r="G150" s="21"/>
-      <c r="H150" s="21"/>
-      <c r="I150" s="19"/>
-      <c r="J150" s="20"/>
+      <c r="C150" s="19"/>
+      <c r="D150" s="19"/>
+      <c r="E150" s="25"/>
+      <c r="F150" s="25"/>
+      <c r="G150" s="19"/>
+      <c r="H150" s="19"/>
+      <c r="I150" s="20"/>
+      <c r="J150" s="24"/>
       <c r="L150" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M150" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N150" s="10"/>
       <c r="O150" s="10"/>
@@ -5855,62 +5855,62 @@
       <c r="Q150" s="10"/>
       <c r="R150" s="10"/>
       <c r="S150" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T150" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U150" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="V150" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="151" spans="2:22">
-      <c r="C151" s="21"/>
-      <c r="D151" s="21"/>
-      <c r="E151" s="22"/>
-      <c r="F151" s="22"/>
-      <c r="G151" s="21"/>
-      <c r="H151" s="21"/>
-      <c r="I151" s="19"/>
-      <c r="J151" s="20"/>
+      <c r="C151" s="19"/>
+      <c r="D151" s="19"/>
+      <c r="E151" s="25"/>
+      <c r="F151" s="25"/>
+      <c r="G151" s="19"/>
+      <c r="H151" s="19"/>
+      <c r="I151" s="20"/>
+      <c r="J151" s="24"/>
       <c r="L151" s="14" t="s">
         <v>17</v>
       </c>
       <c r="M151" s="14"/>
       <c r="N151" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O151" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P151" s="14"/>
       <c r="Q151" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R151" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S151" s="10"/>
       <c r="T151" s="10"/>
       <c r="U151" s="10"/>
     </row>
     <row r="152" spans="2:22">
-      <c r="C152" s="21"/>
-      <c r="D152" s="21"/>
-      <c r="E152" s="22"/>
-      <c r="F152" s="22"/>
-      <c r="G152" s="21"/>
-      <c r="H152" s="21"/>
-      <c r="I152" s="19"/>
-      <c r="J152" s="20"/>
+      <c r="C152" s="19"/>
+      <c r="D152" s="19"/>
+      <c r="E152" s="25"/>
+      <c r="F152" s="25"/>
+      <c r="G152" s="19"/>
+      <c r="H152" s="19"/>
+      <c r="I152" s="20"/>
+      <c r="J152" s="24"/>
       <c r="L152" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M152" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N152" s="10"/>
       <c r="O152" s="10"/>
@@ -5922,26 +5922,26 @@
       <c r="U152" s="10"/>
     </row>
     <row r="153" spans="2:22">
-      <c r="C153" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="D153" s="21"/>
-      <c r="E153" s="22"/>
-      <c r="F153" s="22"/>
-      <c r="G153" s="21"/>
-      <c r="H153" s="21"/>
-      <c r="I153" s="23"/>
-      <c r="J153" s="26" t="s">
-        <v>35</v>
+      <c r="C153" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="D153" s="19"/>
+      <c r="E153" s="25"/>
+      <c r="F153" s="25"/>
+      <c r="G153" s="19"/>
+      <c r="H153" s="19"/>
+      <c r="I153" s="30"/>
+      <c r="J153" s="29" t="s">
+        <v>34</v>
       </c>
       <c r="L153" s="9" t="s">
         <v>0</v>
       </c>
       <c r="M153" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N153" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O153" s="9">
         <v>0</v>
@@ -5956,65 +5956,65 @@
       <c r="U153" s="10"/>
     </row>
     <row r="154" spans="2:22">
-      <c r="C154" s="21"/>
-      <c r="D154" s="21"/>
-      <c r="E154" s="22"/>
-      <c r="F154" s="22"/>
-      <c r="G154" s="21"/>
-      <c r="H154" s="21"/>
-      <c r="I154" s="24"/>
-      <c r="J154" s="26"/>
+      <c r="C154" s="19"/>
+      <c r="D154" s="19"/>
+      <c r="E154" s="25"/>
+      <c r="F154" s="25"/>
+      <c r="G154" s="19"/>
+      <c r="H154" s="19"/>
+      <c r="I154" s="31"/>
+      <c r="J154" s="29"/>
       <c r="L154" s="11" t="s">
         <v>5</v>
       </c>
       <c r="M154" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N154" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O154" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P154" s="11">
         <v>0</v>
       </c>
       <c r="Q154" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R154" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S154" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="T154" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="U154" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="V154" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="155" spans="2:22">
       <c r="B155" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C155" s="21"/>
-      <c r="D155" s="21"/>
-      <c r="E155" s="22"/>
-      <c r="F155" s="22"/>
-      <c r="G155" s="21"/>
-      <c r="H155" s="21"/>
-      <c r="I155" s="24"/>
-      <c r="J155" s="26"/>
+        <v>51</v>
+      </c>
+      <c r="C155" s="19"/>
+      <c r="D155" s="19"/>
+      <c r="E155" s="25"/>
+      <c r="F155" s="25"/>
+      <c r="G155" s="19"/>
+      <c r="H155" s="19"/>
+      <c r="I155" s="31"/>
+      <c r="J155" s="29"/>
       <c r="L155" s="12" t="s">
         <v>15</v>
       </c>
       <c r="M155" s="13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N155" s="10"/>
       <c r="O155" s="10"/>
@@ -6030,14 +6030,14 @@
       <c r="B156">
         <v>7</v>
       </c>
-      <c r="C156" s="21"/>
-      <c r="D156" s="21"/>
-      <c r="E156" s="22"/>
-      <c r="F156" s="22"/>
-      <c r="G156" s="21"/>
-      <c r="H156" s="21"/>
-      <c r="I156" s="24"/>
-      <c r="J156" s="26"/>
+      <c r="C156" s="19"/>
+      <c r="D156" s="19"/>
+      <c r="E156" s="25"/>
+      <c r="F156" s="25"/>
+      <c r="G156" s="19"/>
+      <c r="H156" s="19"/>
+      <c r="I156" s="31"/>
+      <c r="J156" s="29"/>
       <c r="L156" s="14" t="s">
         <v>17</v>
       </c>
@@ -6047,36 +6047,36 @@
         <v>1344</v>
       </c>
       <c r="O156" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P156" s="14"/>
       <c r="Q156" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R156" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S156" s="10"/>
       <c r="T156" s="10"/>
       <c r="U156" s="10"/>
     </row>
     <row r="157" spans="2:22">
-      <c r="C157" s="21"/>
-      <c r="D157" s="21"/>
-      <c r="E157" s="22"/>
-      <c r="F157" s="22"/>
-      <c r="G157" s="21"/>
-      <c r="H157" s="21"/>
-      <c r="I157" s="25"/>
-      <c r="J157" s="26"/>
+      <c r="C157" s="19"/>
+      <c r="D157" s="19"/>
+      <c r="E157" s="25"/>
+      <c r="F157" s="25"/>
+      <c r="G157" s="19"/>
+      <c r="H157" s="19"/>
+      <c r="I157" s="32"/>
+      <c r="J157" s="29"/>
       <c r="L157" s="15" t="s">
         <v>23</v>
       </c>
       <c r="M157" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N157" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O157" s="10"/>
       <c r="P157" s="10"/>
@@ -6088,134 +6088,86 @@
     </row>
   </sheetData>
   <mergeCells count="225">
-    <mergeCell ref="I7:I11"/>
-    <mergeCell ref="J7:J11"/>
-    <mergeCell ref="C12:C16"/>
-    <mergeCell ref="D12:D16"/>
-    <mergeCell ref="E12:E16"/>
-    <mergeCell ref="F12:F16"/>
-    <mergeCell ref="G12:G16"/>
-    <mergeCell ref="H12:H16"/>
-    <mergeCell ref="I12:I16"/>
-    <mergeCell ref="J12:J16"/>
-    <mergeCell ref="C7:C11"/>
-    <mergeCell ref="D7:D11"/>
-    <mergeCell ref="E7:E11"/>
-    <mergeCell ref="F7:F11"/>
-    <mergeCell ref="G7:G11"/>
-    <mergeCell ref="H7:H11"/>
-    <mergeCell ref="I17:I21"/>
-    <mergeCell ref="J17:J21"/>
-    <mergeCell ref="C22:C26"/>
-    <mergeCell ref="D22:D26"/>
-    <mergeCell ref="E22:E26"/>
-    <mergeCell ref="F22:F26"/>
-    <mergeCell ref="G22:G26"/>
-    <mergeCell ref="H22:H26"/>
-    <mergeCell ref="I22:I26"/>
-    <mergeCell ref="J22:J26"/>
-    <mergeCell ref="C17:C21"/>
-    <mergeCell ref="D17:D21"/>
-    <mergeCell ref="E17:E21"/>
-    <mergeCell ref="F17:F21"/>
-    <mergeCell ref="G17:G21"/>
-    <mergeCell ref="H17:H21"/>
-    <mergeCell ref="I29:I33"/>
-    <mergeCell ref="J29:J33"/>
-    <mergeCell ref="C34:C38"/>
-    <mergeCell ref="D34:D38"/>
-    <mergeCell ref="E34:E38"/>
-    <mergeCell ref="F34:F38"/>
-    <mergeCell ref="G34:G38"/>
-    <mergeCell ref="H34:H38"/>
-    <mergeCell ref="I34:I38"/>
-    <mergeCell ref="J34:J38"/>
-    <mergeCell ref="C29:C33"/>
-    <mergeCell ref="D29:D33"/>
-    <mergeCell ref="E29:E33"/>
-    <mergeCell ref="F29:F33"/>
-    <mergeCell ref="G29:G33"/>
-    <mergeCell ref="H29:H33"/>
-    <mergeCell ref="I39:I43"/>
-    <mergeCell ref="J39:J43"/>
-    <mergeCell ref="C45:C49"/>
-    <mergeCell ref="D45:D49"/>
-    <mergeCell ref="E45:E49"/>
-    <mergeCell ref="F45:F49"/>
-    <mergeCell ref="G45:G49"/>
-    <mergeCell ref="H45:H49"/>
-    <mergeCell ref="I45:I49"/>
-    <mergeCell ref="J45:J49"/>
-    <mergeCell ref="C39:C43"/>
-    <mergeCell ref="D39:D43"/>
-    <mergeCell ref="E39:E43"/>
-    <mergeCell ref="F39:F43"/>
-    <mergeCell ref="G39:G43"/>
-    <mergeCell ref="H39:H43"/>
-    <mergeCell ref="I50:I54"/>
-    <mergeCell ref="J50:J54"/>
-    <mergeCell ref="C55:C59"/>
-    <mergeCell ref="D55:D59"/>
-    <mergeCell ref="E55:E59"/>
-    <mergeCell ref="F55:F59"/>
-    <mergeCell ref="G55:G59"/>
-    <mergeCell ref="H55:H59"/>
-    <mergeCell ref="I55:I59"/>
-    <mergeCell ref="J55:J59"/>
-    <mergeCell ref="C50:C54"/>
-    <mergeCell ref="D50:D54"/>
-    <mergeCell ref="E50:E54"/>
-    <mergeCell ref="F50:F54"/>
-    <mergeCell ref="G50:G54"/>
-    <mergeCell ref="H50:H54"/>
-    <mergeCell ref="I61:I65"/>
-    <mergeCell ref="J61:J65"/>
-    <mergeCell ref="C66:C70"/>
-    <mergeCell ref="D66:D70"/>
-    <mergeCell ref="E66:E70"/>
-    <mergeCell ref="F66:F70"/>
-    <mergeCell ref="G66:G70"/>
-    <mergeCell ref="H66:H70"/>
-    <mergeCell ref="I66:I70"/>
-    <mergeCell ref="J66:J70"/>
-    <mergeCell ref="C61:C65"/>
-    <mergeCell ref="D61:D65"/>
-    <mergeCell ref="E61:E65"/>
-    <mergeCell ref="F61:F65"/>
-    <mergeCell ref="G61:G65"/>
-    <mergeCell ref="H61:H65"/>
-    <mergeCell ref="I71:I75"/>
-    <mergeCell ref="J71:J75"/>
-    <mergeCell ref="C77:C81"/>
-    <mergeCell ref="D77:D81"/>
-    <mergeCell ref="E77:E81"/>
-    <mergeCell ref="F77:F81"/>
-    <mergeCell ref="G77:G81"/>
-    <mergeCell ref="H77:H81"/>
-    <mergeCell ref="I77:I81"/>
-    <mergeCell ref="J77:J81"/>
-    <mergeCell ref="C71:C75"/>
-    <mergeCell ref="D71:D75"/>
-    <mergeCell ref="E71:E75"/>
-    <mergeCell ref="F71:F75"/>
-    <mergeCell ref="G71:G75"/>
-    <mergeCell ref="H71:H75"/>
-    <mergeCell ref="I82:I86"/>
-    <mergeCell ref="J82:J86"/>
-    <mergeCell ref="C87:C91"/>
-    <mergeCell ref="D87:D91"/>
-    <mergeCell ref="E87:E91"/>
-    <mergeCell ref="F87:F91"/>
-    <mergeCell ref="G87:G91"/>
-    <mergeCell ref="H87:H91"/>
-    <mergeCell ref="I87:I91"/>
-    <mergeCell ref="J87:J91"/>
-    <mergeCell ref="C82:C86"/>
-    <mergeCell ref="D82:D86"/>
-    <mergeCell ref="E82:E86"/>
-    <mergeCell ref="F82:F86"/>
-    <mergeCell ref="G82:G86"/>
-    <mergeCell ref="H82:H86"/>
+    <mergeCell ref="I148:I152"/>
+    <mergeCell ref="J148:J152"/>
+    <mergeCell ref="C153:C157"/>
+    <mergeCell ref="D153:D157"/>
+    <mergeCell ref="E153:E157"/>
+    <mergeCell ref="F153:F157"/>
+    <mergeCell ref="G153:G157"/>
+    <mergeCell ref="H153:H157"/>
+    <mergeCell ref="I153:I157"/>
+    <mergeCell ref="J153:J157"/>
+    <mergeCell ref="C148:C152"/>
+    <mergeCell ref="D148:D152"/>
+    <mergeCell ref="E148:E152"/>
+    <mergeCell ref="F148:F152"/>
+    <mergeCell ref="G148:G152"/>
+    <mergeCell ref="H148:H152"/>
+    <mergeCell ref="I137:I141"/>
+    <mergeCell ref="J137:J141"/>
+    <mergeCell ref="C143:C147"/>
+    <mergeCell ref="D143:D147"/>
+    <mergeCell ref="E143:E147"/>
+    <mergeCell ref="F143:F147"/>
+    <mergeCell ref="G143:G147"/>
+    <mergeCell ref="H143:H147"/>
+    <mergeCell ref="I143:I147"/>
+    <mergeCell ref="J143:J147"/>
+    <mergeCell ref="C137:C141"/>
+    <mergeCell ref="D137:D141"/>
+    <mergeCell ref="E137:E141"/>
+    <mergeCell ref="F137:F141"/>
+    <mergeCell ref="G137:G141"/>
+    <mergeCell ref="H137:H141"/>
+    <mergeCell ref="I127:I131"/>
+    <mergeCell ref="J127:J131"/>
+    <mergeCell ref="C132:C136"/>
+    <mergeCell ref="D132:D136"/>
+    <mergeCell ref="E132:E136"/>
+    <mergeCell ref="F132:F136"/>
+    <mergeCell ref="G132:G136"/>
+    <mergeCell ref="H132:H136"/>
+    <mergeCell ref="I132:I136"/>
+    <mergeCell ref="J132:J136"/>
+    <mergeCell ref="C127:C131"/>
+    <mergeCell ref="D127:D131"/>
+    <mergeCell ref="E127:E131"/>
+    <mergeCell ref="F127:F131"/>
+    <mergeCell ref="G127:G131"/>
+    <mergeCell ref="H127:H131"/>
+    <mergeCell ref="I116:I120"/>
+    <mergeCell ref="J116:J120"/>
+    <mergeCell ref="C121:C125"/>
+    <mergeCell ref="D121:D125"/>
+    <mergeCell ref="E121:E125"/>
+    <mergeCell ref="F121:F125"/>
+    <mergeCell ref="G121:G125"/>
+    <mergeCell ref="H121:H125"/>
+    <mergeCell ref="I121:I125"/>
+    <mergeCell ref="J121:J125"/>
+    <mergeCell ref="C116:C120"/>
+    <mergeCell ref="D116:D120"/>
+    <mergeCell ref="E116:E120"/>
+    <mergeCell ref="F116:F120"/>
+    <mergeCell ref="G116:G120"/>
+    <mergeCell ref="H116:H120"/>
+    <mergeCell ref="I105:I109"/>
+    <mergeCell ref="J105:J109"/>
+    <mergeCell ref="C111:C115"/>
+    <mergeCell ref="D111:D115"/>
+    <mergeCell ref="E111:E115"/>
+    <mergeCell ref="F111:F115"/>
+    <mergeCell ref="G111:G115"/>
+    <mergeCell ref="H111:H115"/>
+    <mergeCell ref="I111:I115"/>
+    <mergeCell ref="J111:J115"/>
+    <mergeCell ref="C105:C109"/>
+    <mergeCell ref="D105:D109"/>
+    <mergeCell ref="E105:E109"/>
+    <mergeCell ref="F105:F109"/>
+    <mergeCell ref="G105:G109"/>
+    <mergeCell ref="H105:H109"/>
     <mergeCell ref="B94:C94"/>
     <mergeCell ref="I95:I99"/>
     <mergeCell ref="J95:J99"/>
@@ -6233,86 +6185,134 @@
     <mergeCell ref="F95:F99"/>
     <mergeCell ref="G95:G99"/>
     <mergeCell ref="H95:H99"/>
-    <mergeCell ref="I105:I109"/>
-    <mergeCell ref="J105:J109"/>
-    <mergeCell ref="C111:C115"/>
-    <mergeCell ref="D111:D115"/>
-    <mergeCell ref="E111:E115"/>
-    <mergeCell ref="F111:F115"/>
-    <mergeCell ref="G111:G115"/>
-    <mergeCell ref="H111:H115"/>
-    <mergeCell ref="I111:I115"/>
-    <mergeCell ref="J111:J115"/>
-    <mergeCell ref="C105:C109"/>
-    <mergeCell ref="D105:D109"/>
-    <mergeCell ref="E105:E109"/>
-    <mergeCell ref="F105:F109"/>
-    <mergeCell ref="G105:G109"/>
-    <mergeCell ref="H105:H109"/>
-    <mergeCell ref="I116:I120"/>
-    <mergeCell ref="J116:J120"/>
-    <mergeCell ref="C121:C125"/>
-    <mergeCell ref="D121:D125"/>
-    <mergeCell ref="E121:E125"/>
-    <mergeCell ref="F121:F125"/>
-    <mergeCell ref="G121:G125"/>
-    <mergeCell ref="H121:H125"/>
-    <mergeCell ref="I121:I125"/>
-    <mergeCell ref="J121:J125"/>
-    <mergeCell ref="C116:C120"/>
-    <mergeCell ref="D116:D120"/>
-    <mergeCell ref="E116:E120"/>
-    <mergeCell ref="F116:F120"/>
-    <mergeCell ref="G116:G120"/>
-    <mergeCell ref="H116:H120"/>
-    <mergeCell ref="I127:I131"/>
-    <mergeCell ref="J127:J131"/>
-    <mergeCell ref="C132:C136"/>
-    <mergeCell ref="D132:D136"/>
-    <mergeCell ref="E132:E136"/>
-    <mergeCell ref="F132:F136"/>
-    <mergeCell ref="G132:G136"/>
-    <mergeCell ref="H132:H136"/>
-    <mergeCell ref="I132:I136"/>
-    <mergeCell ref="J132:J136"/>
-    <mergeCell ref="C127:C131"/>
-    <mergeCell ref="D127:D131"/>
-    <mergeCell ref="E127:E131"/>
-    <mergeCell ref="F127:F131"/>
-    <mergeCell ref="G127:G131"/>
-    <mergeCell ref="H127:H131"/>
-    <mergeCell ref="I137:I141"/>
-    <mergeCell ref="J137:J141"/>
-    <mergeCell ref="C143:C147"/>
-    <mergeCell ref="D143:D147"/>
-    <mergeCell ref="E143:E147"/>
-    <mergeCell ref="F143:F147"/>
-    <mergeCell ref="G143:G147"/>
-    <mergeCell ref="H143:H147"/>
-    <mergeCell ref="I143:I147"/>
-    <mergeCell ref="J143:J147"/>
-    <mergeCell ref="C137:C141"/>
-    <mergeCell ref="D137:D141"/>
-    <mergeCell ref="E137:E141"/>
-    <mergeCell ref="F137:F141"/>
-    <mergeCell ref="G137:G141"/>
-    <mergeCell ref="H137:H141"/>
-    <mergeCell ref="I148:I152"/>
-    <mergeCell ref="J148:J152"/>
-    <mergeCell ref="C153:C157"/>
-    <mergeCell ref="D153:D157"/>
-    <mergeCell ref="E153:E157"/>
-    <mergeCell ref="F153:F157"/>
-    <mergeCell ref="G153:G157"/>
-    <mergeCell ref="H153:H157"/>
-    <mergeCell ref="I153:I157"/>
-    <mergeCell ref="J153:J157"/>
-    <mergeCell ref="C148:C152"/>
-    <mergeCell ref="D148:D152"/>
-    <mergeCell ref="E148:E152"/>
-    <mergeCell ref="F148:F152"/>
-    <mergeCell ref="G148:G152"/>
-    <mergeCell ref="H148:H152"/>
+    <mergeCell ref="I82:I86"/>
+    <mergeCell ref="J82:J86"/>
+    <mergeCell ref="C87:C91"/>
+    <mergeCell ref="D87:D91"/>
+    <mergeCell ref="E87:E91"/>
+    <mergeCell ref="F87:F91"/>
+    <mergeCell ref="G87:G91"/>
+    <mergeCell ref="H87:H91"/>
+    <mergeCell ref="I87:I91"/>
+    <mergeCell ref="J87:J91"/>
+    <mergeCell ref="C82:C86"/>
+    <mergeCell ref="D82:D86"/>
+    <mergeCell ref="E82:E86"/>
+    <mergeCell ref="F82:F86"/>
+    <mergeCell ref="G82:G86"/>
+    <mergeCell ref="H82:H86"/>
+    <mergeCell ref="I71:I75"/>
+    <mergeCell ref="J71:J75"/>
+    <mergeCell ref="C77:C81"/>
+    <mergeCell ref="D77:D81"/>
+    <mergeCell ref="E77:E81"/>
+    <mergeCell ref="F77:F81"/>
+    <mergeCell ref="G77:G81"/>
+    <mergeCell ref="H77:H81"/>
+    <mergeCell ref="I77:I81"/>
+    <mergeCell ref="J77:J81"/>
+    <mergeCell ref="C71:C75"/>
+    <mergeCell ref="D71:D75"/>
+    <mergeCell ref="E71:E75"/>
+    <mergeCell ref="F71:F75"/>
+    <mergeCell ref="G71:G75"/>
+    <mergeCell ref="H71:H75"/>
+    <mergeCell ref="I61:I65"/>
+    <mergeCell ref="J61:J65"/>
+    <mergeCell ref="C66:C70"/>
+    <mergeCell ref="D66:D70"/>
+    <mergeCell ref="E66:E70"/>
+    <mergeCell ref="F66:F70"/>
+    <mergeCell ref="G66:G70"/>
+    <mergeCell ref="H66:H70"/>
+    <mergeCell ref="I66:I70"/>
+    <mergeCell ref="J66:J70"/>
+    <mergeCell ref="C61:C65"/>
+    <mergeCell ref="D61:D65"/>
+    <mergeCell ref="E61:E65"/>
+    <mergeCell ref="F61:F65"/>
+    <mergeCell ref="G61:G65"/>
+    <mergeCell ref="H61:H65"/>
+    <mergeCell ref="I50:I54"/>
+    <mergeCell ref="J50:J54"/>
+    <mergeCell ref="C55:C59"/>
+    <mergeCell ref="D55:D59"/>
+    <mergeCell ref="E55:E59"/>
+    <mergeCell ref="F55:F59"/>
+    <mergeCell ref="G55:G59"/>
+    <mergeCell ref="H55:H59"/>
+    <mergeCell ref="I55:I59"/>
+    <mergeCell ref="J55:J59"/>
+    <mergeCell ref="C50:C54"/>
+    <mergeCell ref="D50:D54"/>
+    <mergeCell ref="E50:E54"/>
+    <mergeCell ref="F50:F54"/>
+    <mergeCell ref="G50:G54"/>
+    <mergeCell ref="H50:H54"/>
+    <mergeCell ref="I39:I43"/>
+    <mergeCell ref="J39:J43"/>
+    <mergeCell ref="C45:C49"/>
+    <mergeCell ref="D45:D49"/>
+    <mergeCell ref="E45:E49"/>
+    <mergeCell ref="F45:F49"/>
+    <mergeCell ref="G45:G49"/>
+    <mergeCell ref="H45:H49"/>
+    <mergeCell ref="I45:I49"/>
+    <mergeCell ref="J45:J49"/>
+    <mergeCell ref="C39:C43"/>
+    <mergeCell ref="D39:D43"/>
+    <mergeCell ref="E39:E43"/>
+    <mergeCell ref="F39:F43"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="H39:H43"/>
+    <mergeCell ref="I29:I33"/>
+    <mergeCell ref="J29:J33"/>
+    <mergeCell ref="C34:C38"/>
+    <mergeCell ref="D34:D38"/>
+    <mergeCell ref="E34:E38"/>
+    <mergeCell ref="F34:F38"/>
+    <mergeCell ref="G34:G38"/>
+    <mergeCell ref="H34:H38"/>
+    <mergeCell ref="I34:I38"/>
+    <mergeCell ref="J34:J38"/>
+    <mergeCell ref="C29:C33"/>
+    <mergeCell ref="D29:D33"/>
+    <mergeCell ref="E29:E33"/>
+    <mergeCell ref="F29:F33"/>
+    <mergeCell ref="G29:G33"/>
+    <mergeCell ref="H29:H33"/>
+    <mergeCell ref="I17:I21"/>
+    <mergeCell ref="J17:J21"/>
+    <mergeCell ref="C22:C26"/>
+    <mergeCell ref="D22:D26"/>
+    <mergeCell ref="E22:E26"/>
+    <mergeCell ref="F22:F26"/>
+    <mergeCell ref="G22:G26"/>
+    <mergeCell ref="H22:H26"/>
+    <mergeCell ref="I22:I26"/>
+    <mergeCell ref="J22:J26"/>
+    <mergeCell ref="C17:C21"/>
+    <mergeCell ref="D17:D21"/>
+    <mergeCell ref="E17:E21"/>
+    <mergeCell ref="F17:F21"/>
+    <mergeCell ref="G17:G21"/>
+    <mergeCell ref="H17:H21"/>
+    <mergeCell ref="I7:I11"/>
+    <mergeCell ref="J7:J11"/>
+    <mergeCell ref="C12:C16"/>
+    <mergeCell ref="D12:D16"/>
+    <mergeCell ref="E12:E16"/>
+    <mergeCell ref="F12:F16"/>
+    <mergeCell ref="G12:G16"/>
+    <mergeCell ref="H12:H16"/>
+    <mergeCell ref="I12:I16"/>
+    <mergeCell ref="J12:J16"/>
+    <mergeCell ref="C7:C11"/>
+    <mergeCell ref="D7:D11"/>
+    <mergeCell ref="E7:E11"/>
+    <mergeCell ref="F7:F11"/>
+    <mergeCell ref="G7:G11"/>
+    <mergeCell ref="H7:H11"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
